--- a/upload_excel/DigitalData_Test.xlsx
+++ b/upload_excel/DigitalData_Test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CNXK\Downloads\tagging\unpacktoolgit\upload_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyuns\Downloads\unpacktool\unpacktool\upload_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787D0B20-3462-4637-9443-642BFDF8C552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB7CE68-AA75-4837-9DE7-2AA64448AB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DigitalData(author)" sheetId="9" r:id="rId1"/>
@@ -3626,36 +3626,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B536A6-FC45-4277-9276-6B86FB018FC2}">
   <dimension ref="B1:P48"/>
-  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.25" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="70" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="59" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.69921875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="32.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="37.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="8.19921875" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.19921875" style="1"/>
+    <col min="11" max="11" width="15.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="32.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="37.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="8.25" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.25" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.3">
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="2:16" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:16" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>814</v>
       </c>
@@ -3674,7 +3674,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="2:16" s="11" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:16" s="11" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -3686,7 +3686,7 @@
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
     </row>
-    <row r="4" spans="2:16" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:16" ht="52.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="23" t="s">
         <v>0</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="40" t="s">
         <v>854</v>
       </c>
@@ -3754,7 +3754,7 @@
       <c r="O5" s="45"/>
       <c r="P5" s="46"/>
     </row>
-    <row r="6" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="40" t="s">
         <v>855</v>
       </c>
@@ -3775,7 +3775,7 @@
       <c r="O6" s="45"/>
       <c r="P6" s="46"/>
     </row>
-    <row r="7" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="40" t="s">
         <v>856</v>
       </c>
@@ -3796,7 +3796,7 @@
       <c r="O7" s="45"/>
       <c r="P7" s="46"/>
     </row>
-    <row r="8" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="40" t="s">
         <v>857</v>
       </c>
@@ -3817,7 +3817,7 @@
       <c r="O8" s="45"/>
       <c r="P8" s="46"/>
     </row>
-    <row r="9" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="40" t="s">
         <v>858</v>
       </c>
@@ -3838,7 +3838,7 @@
       <c r="O9" s="45"/>
       <c r="P9" s="46"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="40" t="s">
         <v>859</v>
       </c>
@@ -3859,7 +3859,7 @@
       <c r="O10" s="49"/>
       <c r="P10" s="49"/>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="40" t="s">
         <v>860</v>
       </c>
@@ -3880,7 +3880,7 @@
       <c r="O11" s="49"/>
       <c r="P11" s="49"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="49" t="s">
         <v>861</v>
       </c>
@@ -3901,7 +3901,7 @@
       <c r="O12" s="49"/>
       <c r="P12" s="49"/>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="49" t="s">
         <v>862</v>
       </c>
@@ -3922,7 +3922,7 @@
       <c r="O13" s="49"/>
       <c r="P13" s="49"/>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="49" t="s">
         <v>863</v>
       </c>
@@ -3943,7 +3943,7 @@
       <c r="O14" s="49"/>
       <c r="P14" s="49"/>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="49" t="s">
         <v>864</v>
       </c>
@@ -3964,7 +3964,7 @@
       <c r="O15" s="49"/>
       <c r="P15" s="49"/>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="49" t="s">
         <v>865</v>
       </c>
@@ -3985,7 +3985,7 @@
       <c r="O16" s="49"/>
       <c r="P16" s="49"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" s="49" t="s">
         <v>866</v>
       </c>
@@ -4006,7 +4006,7 @@
       <c r="O17" s="49"/>
       <c r="P17" s="49"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" s="49" t="s">
         <v>867</v>
       </c>
@@ -4027,7 +4027,7 @@
       <c r="O18" s="49"/>
       <c r="P18" s="49"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="49" t="s">
         <v>868</v>
       </c>
@@ -4048,7 +4048,7 @@
       <c r="O19" s="49"/>
       <c r="P19" s="49"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="49" t="s">
         <v>869</v>
       </c>
@@ -4069,7 +4069,7 @@
       <c r="O20" s="49"/>
       <c r="P20" s="49"/>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="49" t="s">
         <v>870</v>
       </c>
@@ -4090,7 +4090,7 @@
       <c r="O21" s="49"/>
       <c r="P21" s="49"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" s="49" t="s">
         <v>871</v>
       </c>
@@ -4111,7 +4111,7 @@
       <c r="O22" s="49"/>
       <c r="P22" s="49"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="49" t="s">
         <v>872</v>
       </c>
@@ -4132,7 +4132,7 @@
       <c r="O23" s="49"/>
       <c r="P23" s="49"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" s="49" t="s">
         <v>873</v>
       </c>
@@ -4153,7 +4153,7 @@
       <c r="O24" s="49"/>
       <c r="P24" s="49"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" s="49" t="s">
         <v>874</v>
       </c>
@@ -4174,7 +4174,7 @@
       <c r="O25" s="49"/>
       <c r="P25" s="49"/>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" s="49" t="s">
         <v>875</v>
       </c>
@@ -4195,7 +4195,7 @@
       <c r="O26" s="49"/>
       <c r="P26" s="49"/>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" s="49" t="s">
         <v>876</v>
       </c>
@@ -4216,7 +4216,7 @@
       <c r="O27" s="49"/>
       <c r="P27" s="49"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="49" t="s">
         <v>877</v>
       </c>
@@ -4237,7 +4237,7 @@
       <c r="O28" s="49"/>
       <c r="P28" s="49"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="49" t="s">
         <v>878</v>
       </c>
@@ -4258,7 +4258,7 @@
       <c r="O29" s="49"/>
       <c r="P29" s="49"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="49" t="s">
         <v>879</v>
       </c>
@@ -4279,7 +4279,7 @@
       <c r="O30" s="49"/>
       <c r="P30" s="49"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="49" t="s">
         <v>880</v>
       </c>
@@ -4300,7 +4300,7 @@
       <c r="O31" s="49"/>
       <c r="P31" s="49"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="49" t="s">
         <v>881</v>
       </c>
@@ -4321,7 +4321,7 @@
       <c r="O32" s="49"/>
       <c r="P32" s="49"/>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="49" t="s">
         <v>882</v>
       </c>
@@ -4342,7 +4342,7 @@
       <c r="O33" s="49"/>
       <c r="P33" s="49"/>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B34" s="49" t="s">
         <v>883</v>
       </c>
@@ -4363,7 +4363,7 @@
       <c r="O34" s="49"/>
       <c r="P34" s="49"/>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="49" t="s">
         <v>884</v>
       </c>
@@ -4384,7 +4384,7 @@
       <c r="O35" s="49"/>
       <c r="P35" s="49"/>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="49" t="s">
         <v>885</v>
       </c>
@@ -4405,7 +4405,7 @@
       <c r="O36" s="49"/>
       <c r="P36" s="49"/>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="49" t="s">
         <v>886</v>
       </c>
@@ -4426,7 +4426,7 @@
       <c r="O37" s="49"/>
       <c r="P37" s="49"/>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="49" t="s">
         <v>887</v>
       </c>
@@ -4447,7 +4447,7 @@
       <c r="O38" s="49"/>
       <c r="P38" s="49"/>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="49" t="s">
         <v>888</v>
       </c>
@@ -4468,7 +4468,7 @@
       <c r="O39" s="49"/>
       <c r="P39" s="49"/>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B40" s="49" t="s">
         <v>889</v>
       </c>
@@ -4489,7 +4489,7 @@
       <c r="O40" s="49"/>
       <c r="P40" s="49"/>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="49" t="s">
         <v>890</v>
       </c>
@@ -4510,7 +4510,7 @@
       <c r="O41" s="49"/>
       <c r="P41" s="49"/>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" s="49" t="s">
         <v>891</v>
       </c>
@@ -4531,7 +4531,7 @@
       <c r="O42" s="49"/>
       <c r="P42" s="49"/>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" s="49" t="s">
         <v>892</v>
       </c>
@@ -4552,7 +4552,7 @@
       <c r="O43" s="49"/>
       <c r="P43" s="49"/>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" s="49" t="s">
         <v>893</v>
       </c>
@@ -4573,7 +4573,7 @@
       <c r="O44" s="49"/>
       <c r="P44" s="49"/>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B45" s="49" t="s">
         <v>894</v>
       </c>
@@ -4594,7 +4594,7 @@
       <c r="O45" s="49"/>
       <c r="P45" s="49"/>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B46" s="49" t="s">
         <v>895</v>
       </c>
@@ -4615,7 +4615,7 @@
       <c r="O46" s="49"/>
       <c r="P46" s="49"/>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="49" t="s">
         <v>896</v>
       </c>
@@ -4636,7 +4636,7 @@
       <c r="O47" s="49"/>
       <c r="P47" s="49"/>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="49" t="s">
         <v>897</v>
       </c>
@@ -4667,36 +4667,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DD3D6A0-AA1B-4411-8FD3-FFBEDBC60F3A}">
   <dimension ref="B1:P41"/>
-  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.25" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="70" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="59" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.69921875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="32.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="37.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="8.19921875" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.19921875" style="1"/>
+    <col min="11" max="11" width="15.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="32.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="37.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="8.25" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.25" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.3">
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="2:16" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:16" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>814</v>
       </c>
@@ -4715,7 +4715,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="2:16" s="11" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:16" s="11" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -4727,7 +4727,7 @@
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
     </row>
-    <row r="4" spans="2:16" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:16" ht="52.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="23" t="s">
         <v>0</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="40" t="s">
         <v>36</v>
       </c>
@@ -4795,7 +4795,7 @@
       <c r="O5" s="17"/>
       <c r="P5" s="35"/>
     </row>
-    <row r="6" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="40" t="s">
         <v>37</v>
       </c>
@@ -4816,7 +4816,7 @@
       <c r="O6" s="17"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="40" t="s">
         <v>40</v>
       </c>
@@ -4837,7 +4837,7 @@
       <c r="O7" s="17"/>
       <c r="P7" s="18"/>
     </row>
-    <row r="8" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="40" t="s">
         <v>41</v>
       </c>
@@ -4858,7 +4858,7 @@
       <c r="O8" s="17"/>
       <c r="P8" s="18"/>
     </row>
-    <row r="9" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="40" t="s">
         <v>43</v>
       </c>
@@ -4879,7 +4879,7 @@
       <c r="O9" s="17"/>
       <c r="P9" s="18"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="40" t="s">
         <v>45</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="40" t="s">
         <v>46</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="40" t="s">
         <v>48</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="40" t="s">
         <v>52</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="40" t="s">
         <v>55</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="40" t="s">
         <v>56</v>
       </c>
@@ -4939,7 +4939,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="40" t="s">
         <v>58</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="40" t="s">
         <v>60</v>
       </c>
@@ -4959,7 +4959,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="40" t="s">
         <v>61</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="40" t="s">
         <v>63</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="40" t="s">
         <v>64</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="40" t="s">
         <v>67</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="40" t="s">
         <v>68</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="40" t="s">
         <v>69</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="40" t="s">
         <v>83</v>
       </c>
@@ -5029,7 +5029,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="40" t="s">
         <v>85</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="40" t="s">
         <v>88</v>
       </c>
@@ -5049,7 +5049,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="40" t="s">
         <v>96</v>
       </c>
@@ -5059,7 +5059,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="40" t="s">
         <v>97</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="40" t="s">
         <v>100</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="40" t="s">
         <v>101</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="40" t="s">
         <v>31</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="40" t="s">
         <v>106</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="40" t="s">
         <v>107</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="40" t="s">
         <v>108</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="40" t="s">
         <v>109</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="40" t="s">
         <v>110</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="40" t="s">
         <v>112</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="40" t="s">
         <v>113</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="40" t="s">
         <v>114</v>
       </c>
@@ -5179,7 +5179,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="40" t="s">
         <v>115</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="40" t="s">
         <v>121</v>
       </c>
@@ -5209,36 +5209,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:P399"/>
-  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.25" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="70" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="59" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.09765625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="32.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="37.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="8.19921875" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.19921875" style="1"/>
+    <col min="11" max="11" width="17.125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="32.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="37.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="8.25" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.25" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
@@ -5257,7 +5257,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" s="11" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" s="11" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -5269,7 +5269,7 @@
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
     </row>
-    <row r="4" spans="1:16" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="52.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="23" t="s">
         <v>0</v>
       </c>
@@ -5316,7 +5316,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12" t="s">
         <v>2</v>
       </c>
@@ -5337,7 +5337,7 @@
       <c r="O5" s="17"/>
       <c r="P5" s="35"/>
     </row>
-    <row r="6" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="16" t="s">
         <v>2</v>
       </c>
@@ -5358,7 +5358,7 @@
       <c r="O6" s="17"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
         <v>2</v>
       </c>
@@ -5379,7 +5379,7 @@
       <c r="O7" s="17"/>
       <c r="P7" s="18"/>
     </row>
-    <row r="8" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
         <v>2</v>
       </c>
@@ -5400,7 +5400,7 @@
       <c r="O8" s="17"/>
       <c r="P8" s="18"/>
     </row>
-    <row r="9" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
         <v>3</v>
       </c>
@@ -5421,7 +5421,7 @@
       <c r="O9" s="17"/>
       <c r="P9" s="18"/>
     </row>
-    <row r="10" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -5445,7 +5445,7 @@
       <c r="O10" s="17"/>
       <c r="P10" s="18"/>
     </row>
-    <row r="11" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
         <v>3</v>
       </c>
@@ -5466,7 +5466,7 @@
       <c r="O11" s="17"/>
       <c r="P11" s="18"/>
     </row>
-    <row r="12" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="16" t="s">
         <v>3</v>
       </c>
@@ -5487,7 +5487,7 @@
       <c r="O12" s="17"/>
       <c r="P12" s="18"/>
     </row>
-    <row r="13" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="16" t="s">
         <v>4</v>
       </c>
@@ -5508,7 +5508,7 @@
       <c r="O13" s="17"/>
       <c r="P13" s="18"/>
     </row>
-    <row r="14" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
         <v>4</v>
       </c>
@@ -5529,7 +5529,7 @@
       <c r="O14" s="17"/>
       <c r="P14" s="18"/>
     </row>
-    <row r="15" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
         <v>4</v>
       </c>
@@ -5550,7 +5550,7 @@
       <c r="O15" s="17"/>
       <c r="P15" s="18"/>
     </row>
-    <row r="16" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="16" t="s">
         <v>4</v>
       </c>
@@ -5571,7 +5571,7 @@
       <c r="O16" s="17"/>
       <c r="P16" s="18"/>
     </row>
-    <row r="17" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="16" t="s">
         <v>5</v>
       </c>
@@ -5592,7 +5592,7 @@
       <c r="O17" s="17"/>
       <c r="P17" s="18"/>
     </row>
-    <row r="18" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="16" t="s">
         <v>5</v>
       </c>
@@ -5613,7 +5613,7 @@
       <c r="O18" s="17"/>
       <c r="P18" s="18"/>
     </row>
-    <row r="19" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="16" t="s">
         <v>5</v>
       </c>
@@ -5634,7 +5634,7 @@
       <c r="O19" s="17"/>
       <c r="P19" s="18"/>
     </row>
-    <row r="20" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="16" t="s">
         <v>5</v>
       </c>
@@ -5655,7 +5655,7 @@
       <c r="O20" s="17"/>
       <c r="P20" s="18"/>
     </row>
-    <row r="21" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="16" t="s">
         <v>6</v>
       </c>
@@ -5676,7 +5676,7 @@
       <c r="O21" s="17"/>
       <c r="P21" s="18"/>
     </row>
-    <row r="22" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="16" t="s">
         <v>6</v>
       </c>
@@ -5697,7 +5697,7 @@
       <c r="O22" s="17"/>
       <c r="P22" s="18"/>
     </row>
-    <row r="23" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="16" t="s">
         <v>6</v>
       </c>
@@ -5720,7 +5720,7 @@
       <c r="O23" s="17"/>
       <c r="P23" s="18"/>
     </row>
-    <row r="24" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="16" t="s">
         <v>6</v>
       </c>
@@ -5741,7 +5741,7 @@
       <c r="O24" s="17"/>
       <c r="P24" s="18"/>
     </row>
-    <row r="25" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>36</v>
       </c>
@@ -5762,7 +5762,7 @@
       <c r="O25" s="17"/>
       <c r="P25" s="18"/>
     </row>
-    <row r="26" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="16" t="s">
         <v>36</v>
       </c>
@@ -5783,7 +5783,7 @@
       <c r="O26" s="17"/>
       <c r="P26" s="18"/>
     </row>
-    <row r="27" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="16" t="s">
         <v>36</v>
       </c>
@@ -5804,7 +5804,7 @@
       <c r="O27" s="17"/>
       <c r="P27" s="18"/>
     </row>
-    <row r="28" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="16" t="s">
         <v>36</v>
       </c>
@@ -5825,7 +5825,7 @@
       <c r="O28" s="17"/>
       <c r="P28" s="18"/>
     </row>
-    <row r="29" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="16" t="s">
         <v>37</v>
       </c>
@@ -5846,7 +5846,7 @@
       <c r="O29" s="17"/>
       <c r="P29" s="18"/>
     </row>
-    <row r="30" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="16" t="s">
         <v>37</v>
       </c>
@@ -5867,7 +5867,7 @@
       <c r="O30" s="17"/>
       <c r="P30" s="18"/>
     </row>
-    <row r="31" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="16" t="s">
         <v>37</v>
       </c>
@@ -5888,7 +5888,7 @@
       <c r="O31" s="17"/>
       <c r="P31" s="18"/>
     </row>
-    <row r="32" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="16" t="s">
         <v>37</v>
       </c>
@@ -5909,7 +5909,7 @@
       <c r="O32" s="17"/>
       <c r="P32" s="18"/>
     </row>
-    <row r="33" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="16" t="s">
         <v>38</v>
       </c>
@@ -5930,7 +5930,7 @@
       <c r="O33" s="17"/>
       <c r="P33" s="18"/>
     </row>
-    <row r="34" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="16" t="s">
         <v>38</v>
       </c>
@@ -5951,7 +5951,7 @@
       <c r="O34" s="17"/>
       <c r="P34" s="18"/>
     </row>
-    <row r="35" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="16" t="s">
         <v>38</v>
       </c>
@@ -5972,7 +5972,7 @@
       <c r="O35" s="17"/>
       <c r="P35" s="18"/>
     </row>
-    <row r="36" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="16" t="s">
         <v>38</v>
       </c>
@@ -5993,7 +5993,7 @@
       <c r="O36" s="17"/>
       <c r="P36" s="18"/>
     </row>
-    <row r="37" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="16" t="s">
         <v>39</v>
       </c>
@@ -6014,7 +6014,7 @@
       <c r="O37" s="17"/>
       <c r="P37" s="18"/>
     </row>
-    <row r="38" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="16" t="s">
         <v>39</v>
       </c>
@@ -6035,7 +6035,7 @@
       <c r="O38" s="17"/>
       <c r="P38" s="18"/>
     </row>
-    <row r="39" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="16" t="s">
         <v>39</v>
       </c>
@@ -6056,7 +6056,7 @@
       <c r="O39" s="17"/>
       <c r="P39" s="18"/>
     </row>
-    <row r="40" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="16" t="s">
         <v>39</v>
       </c>
@@ -6077,7 +6077,7 @@
       <c r="O40" s="17"/>
       <c r="P40" s="18"/>
     </row>
-    <row r="41" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="16" t="s">
         <v>40</v>
       </c>
@@ -6098,7 +6098,7 @@
       <c r="O41" s="17"/>
       <c r="P41" s="18"/>
     </row>
-    <row r="42" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="16" t="s">
         <v>40</v>
       </c>
@@ -6119,7 +6119,7 @@
       <c r="O42" s="17"/>
       <c r="P42" s="18"/>
     </row>
-    <row r="43" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="16" t="s">
         <v>40</v>
       </c>
@@ -6140,7 +6140,7 @@
       <c r="O43" s="17"/>
       <c r="P43" s="18"/>
     </row>
-    <row r="44" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="16" t="s">
         <v>40</v>
       </c>
@@ -6161,7 +6161,7 @@
       <c r="O44" s="17"/>
       <c r="P44" s="18"/>
     </row>
-    <row r="45" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="16" t="s">
         <v>41</v>
       </c>
@@ -6182,7 +6182,7 @@
       <c r="O45" s="17"/>
       <c r="P45" s="18"/>
     </row>
-    <row r="46" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="16" t="s">
         <v>41</v>
       </c>
@@ -6203,7 +6203,7 @@
       <c r="O46" s="17"/>
       <c r="P46" s="18"/>
     </row>
-    <row r="47" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="16" t="s">
         <v>41</v>
       </c>
@@ -6224,7 +6224,7 @@
       <c r="O47" s="17"/>
       <c r="P47" s="18"/>
     </row>
-    <row r="48" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="16" t="s">
         <v>41</v>
       </c>
@@ -6245,7 +6245,7 @@
       <c r="O48" s="17"/>
       <c r="P48" s="18"/>
     </row>
-    <row r="49" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="16" t="s">
         <v>42</v>
       </c>
@@ -6266,7 +6266,7 @@
       <c r="O49" s="17"/>
       <c r="P49" s="18"/>
     </row>
-    <row r="50" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="16" t="s">
         <v>42</v>
       </c>
@@ -6287,7 +6287,7 @@
       <c r="O50" s="17"/>
       <c r="P50" s="18"/>
     </row>
-    <row r="51" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="16" t="s">
         <v>42</v>
       </c>
@@ -6308,7 +6308,7 @@
       <c r="O51" s="17"/>
       <c r="P51" s="18"/>
     </row>
-    <row r="52" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="16" t="s">
         <v>42</v>
       </c>
@@ -6329,7 +6329,7 @@
       <c r="O52" s="17"/>
       <c r="P52" s="18"/>
     </row>
-    <row r="53" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="16" t="s">
         <v>43</v>
       </c>
@@ -6350,7 +6350,7 @@
       <c r="O53" s="17"/>
       <c r="P53" s="18"/>
     </row>
-    <row r="54" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="16" t="s">
         <v>43</v>
       </c>
@@ -6371,7 +6371,7 @@
       <c r="O54" s="17"/>
       <c r="P54" s="18"/>
     </row>
-    <row r="55" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="16" t="s">
         <v>43</v>
       </c>
@@ -6392,7 +6392,7 @@
       <c r="O55" s="17"/>
       <c r="P55" s="18"/>
     </row>
-    <row r="56" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="16" t="s">
         <v>43</v>
       </c>
@@ -6413,7 +6413,7 @@
       <c r="O56" s="17"/>
       <c r="P56" s="18"/>
     </row>
-    <row r="57" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="16" t="s">
         <v>44</v>
       </c>
@@ -6434,7 +6434,7 @@
       <c r="O57" s="17"/>
       <c r="P57" s="18"/>
     </row>
-    <row r="58" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="16" t="s">
         <v>44</v>
       </c>
@@ -6455,7 +6455,7 @@
       <c r="O58" s="17"/>
       <c r="P58" s="18"/>
     </row>
-    <row r="59" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="16" t="s">
         <v>44</v>
       </c>
@@ -6476,7 +6476,7 @@
       <c r="O59" s="17"/>
       <c r="P59" s="18"/>
     </row>
-    <row r="60" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="16" t="s">
         <v>44</v>
       </c>
@@ -6497,7 +6497,7 @@
       <c r="O60" s="17"/>
       <c r="P60" s="18"/>
     </row>
-    <row r="61" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="16" t="s">
         <v>45</v>
       </c>
@@ -6518,7 +6518,7 @@
       <c r="O61" s="17"/>
       <c r="P61" s="18"/>
     </row>
-    <row r="62" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="16" t="s">
         <v>45</v>
       </c>
@@ -6539,7 +6539,7 @@
       <c r="O62" s="17"/>
       <c r="P62" s="18"/>
     </row>
-    <row r="63" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="16" t="s">
         <v>45</v>
       </c>
@@ -6560,7 +6560,7 @@
       <c r="O63" s="17"/>
       <c r="P63" s="18"/>
     </row>
-    <row r="64" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="16" t="s">
         <v>45</v>
       </c>
@@ -6581,7 +6581,7 @@
       <c r="O64" s="17"/>
       <c r="P64" s="18"/>
     </row>
-    <row r="65" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="16" t="s">
         <v>46</v>
       </c>
@@ -6602,7 +6602,7 @@
       <c r="O65" s="17"/>
       <c r="P65" s="18"/>
     </row>
-    <row r="66" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="16" t="s">
         <v>46</v>
       </c>
@@ -6623,7 +6623,7 @@
       <c r="O66" s="17"/>
       <c r="P66" s="18"/>
     </row>
-    <row r="67" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="16" t="s">
         <v>46</v>
       </c>
@@ -6644,7 +6644,7 @@
       <c r="O67" s="17"/>
       <c r="P67" s="18"/>
     </row>
-    <row r="68" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="16" t="s">
         <v>46</v>
       </c>
@@ -6665,7 +6665,7 @@
       <c r="O68" s="17"/>
       <c r="P68" s="18"/>
     </row>
-    <row r="69" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="16" t="s">
         <v>47</v>
       </c>
@@ -6686,7 +6686,7 @@
       <c r="O69" s="17"/>
       <c r="P69" s="18"/>
     </row>
-    <row r="70" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="16" t="s">
         <v>47</v>
       </c>
@@ -6707,7 +6707,7 @@
       <c r="O70" s="17"/>
       <c r="P70" s="18"/>
     </row>
-    <row r="71" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="16" t="s">
         <v>47</v>
       </c>
@@ -6728,7 +6728,7 @@
       <c r="O71" s="17"/>
       <c r="P71" s="18"/>
     </row>
-    <row r="72" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="16" t="s">
         <v>47</v>
       </c>
@@ -6749,7 +6749,7 @@
       <c r="O72" s="17"/>
       <c r="P72" s="18"/>
     </row>
-    <row r="73" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="16" t="s">
         <v>48</v>
       </c>
@@ -6770,7 +6770,7 @@
       <c r="O73" s="17"/>
       <c r="P73" s="18"/>
     </row>
-    <row r="74" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="16" t="s">
         <v>48</v>
       </c>
@@ -6791,7 +6791,7 @@
       <c r="O74" s="17"/>
       <c r="P74" s="18"/>
     </row>
-    <row r="75" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="16" t="s">
         <v>48</v>
       </c>
@@ -6812,7 +6812,7 @@
       <c r="O75" s="17"/>
       <c r="P75" s="18"/>
     </row>
-    <row r="76" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="16" t="s">
         <v>49</v>
       </c>
@@ -6833,7 +6833,7 @@
       <c r="O76" s="17"/>
       <c r="P76" s="18"/>
     </row>
-    <row r="77" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="16" t="s">
         <v>49</v>
       </c>
@@ -6854,7 +6854,7 @@
       <c r="O77" s="17"/>
       <c r="P77" s="18"/>
     </row>
-    <row r="78" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="16" t="s">
         <v>49</v>
       </c>
@@ -6875,7 +6875,7 @@
       <c r="O78" s="17"/>
       <c r="P78" s="18"/>
     </row>
-    <row r="79" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
         <v>49</v>
       </c>
@@ -6896,7 +6896,7 @@
       <c r="O79" s="17"/>
       <c r="P79" s="18"/>
     </row>
-    <row r="80" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="16" t="s">
         <v>50</v>
       </c>
@@ -6917,7 +6917,7 @@
       <c r="O80" s="17"/>
       <c r="P80" s="18"/>
     </row>
-    <row r="81" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="16" t="s">
         <v>50</v>
       </c>
@@ -6938,7 +6938,7 @@
       <c r="O81" s="17"/>
       <c r="P81" s="18"/>
     </row>
-    <row r="82" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="16" t="s">
         <v>50</v>
       </c>
@@ -6959,7 +6959,7 @@
       <c r="O82" s="17"/>
       <c r="P82" s="18"/>
     </row>
-    <row r="83" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="16" t="s">
         <v>50</v>
       </c>
@@ -6980,7 +6980,7 @@
       <c r="O83" s="17"/>
       <c r="P83" s="18"/>
     </row>
-    <row r="84" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="16" t="s">
         <v>51</v>
       </c>
@@ -7001,7 +7001,7 @@
       <c r="O84" s="17"/>
       <c r="P84" s="18"/>
     </row>
-    <row r="85" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="16" t="s">
         <v>51</v>
       </c>
@@ -7022,7 +7022,7 @@
       <c r="O85" s="17"/>
       <c r="P85" s="18"/>
     </row>
-    <row r="86" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="16" t="s">
         <v>51</v>
       </c>
@@ -7043,7 +7043,7 @@
       <c r="O86" s="17"/>
       <c r="P86" s="18"/>
     </row>
-    <row r="87" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="16" t="s">
         <v>51</v>
       </c>
@@ -7064,7 +7064,7 @@
       <c r="O87" s="17"/>
       <c r="P87" s="18"/>
     </row>
-    <row r="88" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="16" t="s">
         <v>52</v>
       </c>
@@ -7085,7 +7085,7 @@
       <c r="O88" s="17"/>
       <c r="P88" s="18"/>
     </row>
-    <row r="89" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="16" t="s">
         <v>52</v>
       </c>
@@ -7106,7 +7106,7 @@
       <c r="O89" s="17"/>
       <c r="P89" s="18"/>
     </row>
-    <row r="90" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="16" t="s">
         <v>52</v>
       </c>
@@ -7127,7 +7127,7 @@
       <c r="O90" s="17"/>
       <c r="P90" s="18"/>
     </row>
-    <row r="91" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="16" t="s">
         <v>52</v>
       </c>
@@ -7148,7 +7148,7 @@
       <c r="O91" s="17"/>
       <c r="P91" s="18"/>
     </row>
-    <row r="92" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="16" t="s">
         <v>53</v>
       </c>
@@ -7169,7 +7169,7 @@
       <c r="O92" s="17"/>
       <c r="P92" s="18"/>
     </row>
-    <row r="93" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="16" t="s">
         <v>53</v>
       </c>
@@ -7190,7 +7190,7 @@
       <c r="O93" s="17"/>
       <c r="P93" s="18"/>
     </row>
-    <row r="94" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="16" t="s">
         <v>53</v>
       </c>
@@ -7211,7 +7211,7 @@
       <c r="O94" s="17"/>
       <c r="P94" s="18"/>
     </row>
-    <row r="95" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="16" t="s">
         <v>53</v>
       </c>
@@ -7232,7 +7232,7 @@
       <c r="O95" s="17"/>
       <c r="P95" s="18"/>
     </row>
-    <row r="96" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="16" t="s">
         <v>54</v>
       </c>
@@ -7253,7 +7253,7 @@
       <c r="O96" s="17"/>
       <c r="P96" s="18"/>
     </row>
-    <row r="97" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="16" t="s">
         <v>54</v>
       </c>
@@ -7274,7 +7274,7 @@
       <c r="O97" s="17"/>
       <c r="P97" s="18"/>
     </row>
-    <row r="98" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="16" t="s">
         <v>54</v>
       </c>
@@ -7295,7 +7295,7 @@
       <c r="O98" s="17"/>
       <c r="P98" s="18"/>
     </row>
-    <row r="99" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="16" t="s">
         <v>54</v>
       </c>
@@ -7316,7 +7316,7 @@
       <c r="O99" s="17"/>
       <c r="P99" s="18"/>
     </row>
-    <row r="100" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="16" t="s">
         <v>55</v>
       </c>
@@ -7337,7 +7337,7 @@
       <c r="O100" s="17"/>
       <c r="P100" s="18"/>
     </row>
-    <row r="101" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="16" t="s">
         <v>55</v>
       </c>
@@ -7358,7 +7358,7 @@
       <c r="O101" s="17"/>
       <c r="P101" s="18"/>
     </row>
-    <row r="102" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="16" t="s">
         <v>55</v>
       </c>
@@ -7379,7 +7379,7 @@
       <c r="O102" s="17"/>
       <c r="P102" s="18"/>
     </row>
-    <row r="103" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="16" t="s">
         <v>55</v>
       </c>
@@ -7400,7 +7400,7 @@
       <c r="O103" s="17"/>
       <c r="P103" s="18"/>
     </row>
-    <row r="104" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="16" t="s">
         <v>56</v>
       </c>
@@ -7421,7 +7421,7 @@
       <c r="O104" s="17"/>
       <c r="P104" s="18"/>
     </row>
-    <row r="105" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="16" t="s">
         <v>56</v>
       </c>
@@ -7442,7 +7442,7 @@
       <c r="O105" s="17"/>
       <c r="P105" s="18"/>
     </row>
-    <row r="106" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="16" t="s">
         <v>56</v>
       </c>
@@ -7463,7 +7463,7 @@
       <c r="O106" s="17"/>
       <c r="P106" s="18"/>
     </row>
-    <row r="107" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="16" t="s">
         <v>56</v>
       </c>
@@ -7484,7 +7484,7 @@
       <c r="O107" s="17"/>
       <c r="P107" s="18"/>
     </row>
-    <row r="108" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="16" t="s">
         <v>57</v>
       </c>
@@ -7505,7 +7505,7 @@
       <c r="O108" s="17"/>
       <c r="P108" s="18"/>
     </row>
-    <row r="109" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="16" t="s">
         <v>57</v>
       </c>
@@ -7526,7 +7526,7 @@
       <c r="O109" s="17"/>
       <c r="P109" s="18"/>
     </row>
-    <row r="110" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="16" t="s">
         <v>57</v>
       </c>
@@ -7547,7 +7547,7 @@
       <c r="O110" s="17"/>
       <c r="P110" s="18"/>
     </row>
-    <row r="111" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="16" t="s">
         <v>58</v>
       </c>
@@ -7568,7 +7568,7 @@
       <c r="O111" s="17"/>
       <c r="P111" s="18"/>
     </row>
-    <row r="112" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="16" t="s">
         <v>58</v>
       </c>
@@ -7589,7 +7589,7 @@
       <c r="O112" s="17"/>
       <c r="P112" s="18"/>
     </row>
-    <row r="113" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="16" t="s">
         <v>58</v>
       </c>
@@ -7610,7 +7610,7 @@
       <c r="O113" s="17"/>
       <c r="P113" s="18"/>
     </row>
-    <row r="114" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="16" t="s">
         <v>58</v>
       </c>
@@ -7631,7 +7631,7 @@
       <c r="O114" s="17"/>
       <c r="P114" s="18"/>
     </row>
-    <row r="115" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="16" t="s">
         <v>59</v>
       </c>
@@ -7652,7 +7652,7 @@
       <c r="O115" s="17"/>
       <c r="P115" s="18"/>
     </row>
-    <row r="116" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="16" t="s">
         <v>59</v>
       </c>
@@ -7673,7 +7673,7 @@
       <c r="O116" s="17"/>
       <c r="P116" s="18"/>
     </row>
-    <row r="117" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="16" t="s">
         <v>59</v>
       </c>
@@ -7694,7 +7694,7 @@
       <c r="O117" s="17"/>
       <c r="P117" s="18"/>
     </row>
-    <row r="118" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="16" t="s">
         <v>59</v>
       </c>
@@ -7715,7 +7715,7 @@
       <c r="O118" s="17"/>
       <c r="P118" s="18"/>
     </row>
-    <row r="119" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="16" t="s">
         <v>60</v>
       </c>
@@ -7736,7 +7736,7 @@
       <c r="O119" s="17"/>
       <c r="P119" s="18"/>
     </row>
-    <row r="120" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="16" t="s">
         <v>60</v>
       </c>
@@ -7757,7 +7757,7 @@
       <c r="O120" s="17"/>
       <c r="P120" s="18"/>
     </row>
-    <row r="121" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B121" s="16" t="s">
         <v>60</v>
       </c>
@@ -7778,7 +7778,7 @@
       <c r="O121" s="17"/>
       <c r="P121" s="18"/>
     </row>
-    <row r="122" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="16" t="s">
         <v>60</v>
       </c>
@@ -7799,7 +7799,7 @@
       <c r="O122" s="17"/>
       <c r="P122" s="18"/>
     </row>
-    <row r="123" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="16" t="s">
         <v>61</v>
       </c>
@@ -7820,7 +7820,7 @@
       <c r="O123" s="17"/>
       <c r="P123" s="18"/>
     </row>
-    <row r="124" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="16" t="s">
         <v>61</v>
       </c>
@@ -7841,7 +7841,7 @@
       <c r="O124" s="17"/>
       <c r="P124" s="18"/>
     </row>
-    <row r="125" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B125" s="16" t="s">
         <v>61</v>
       </c>
@@ -7862,7 +7862,7 @@
       <c r="O125" s="17"/>
       <c r="P125" s="18"/>
     </row>
-    <row r="126" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="16" t="s">
         <v>61</v>
       </c>
@@ -7883,7 +7883,7 @@
       <c r="O126" s="17"/>
       <c r="P126" s="18"/>
     </row>
-    <row r="127" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B127" s="16" t="s">
         <v>62</v>
       </c>
@@ -7904,7 +7904,7 @@
       <c r="O127" s="17"/>
       <c r="P127" s="18"/>
     </row>
-    <row r="128" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B128" s="16" t="s">
         <v>62</v>
       </c>
@@ -7925,7 +7925,7 @@
       <c r="O128" s="17"/>
       <c r="P128" s="18"/>
     </row>
-    <row r="129" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B129" s="16" t="s">
         <v>62</v>
       </c>
@@ -7946,7 +7946,7 @@
       <c r="O129" s="17"/>
       <c r="P129" s="18"/>
     </row>
-    <row r="130" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B130" s="16" t="s">
         <v>62</v>
       </c>
@@ -7967,7 +7967,7 @@
       <c r="O130" s="17"/>
       <c r="P130" s="18"/>
     </row>
-    <row r="131" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B131" s="16" t="s">
         <v>63</v>
       </c>
@@ -7988,7 +7988,7 @@
       <c r="O131" s="17"/>
       <c r="P131" s="18"/>
     </row>
-    <row r="132" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B132" s="16" t="s">
         <v>63</v>
       </c>
@@ -8009,7 +8009,7 @@
       <c r="O132" s="17"/>
       <c r="P132" s="18"/>
     </row>
-    <row r="133" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B133" s="16" t="s">
         <v>63</v>
       </c>
@@ -8030,7 +8030,7 @@
       <c r="O133" s="17"/>
       <c r="P133" s="18"/>
     </row>
-    <row r="134" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B134" s="16" t="s">
         <v>63</v>
       </c>
@@ -8051,7 +8051,7 @@
       <c r="O134" s="17"/>
       <c r="P134" s="18"/>
     </row>
-    <row r="135" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B135" s="16" t="s">
         <v>64</v>
       </c>
@@ -8072,7 +8072,7 @@
       <c r="O135" s="17"/>
       <c r="P135" s="18"/>
     </row>
-    <row r="136" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B136" s="16" t="s">
         <v>64</v>
       </c>
@@ -8093,7 +8093,7 @@
       <c r="O136" s="17"/>
       <c r="P136" s="18"/>
     </row>
-    <row r="137" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B137" s="16" t="s">
         <v>64</v>
       </c>
@@ -8114,7 +8114,7 @@
       <c r="O137" s="17"/>
       <c r="P137" s="18"/>
     </row>
-    <row r="138" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B138" s="16" t="s">
         <v>64</v>
       </c>
@@ -8135,7 +8135,7 @@
       <c r="O138" s="17"/>
       <c r="P138" s="18"/>
     </row>
-    <row r="139" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B139" s="16" t="s">
         <v>65</v>
       </c>
@@ -8156,7 +8156,7 @@
       <c r="O139" s="17"/>
       <c r="P139" s="18"/>
     </row>
-    <row r="140" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="16" t="s">
         <v>65</v>
       </c>
@@ -8177,7 +8177,7 @@
       <c r="O140" s="17"/>
       <c r="P140" s="18"/>
     </row>
-    <row r="141" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="16" t="s">
         <v>65</v>
       </c>
@@ -8198,7 +8198,7 @@
       <c r="O141" s="17"/>
       <c r="P141" s="18"/>
     </row>
-    <row r="142" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B142" s="16" t="s">
         <v>65</v>
       </c>
@@ -8219,7 +8219,7 @@
       <c r="O142" s="17"/>
       <c r="P142" s="18"/>
     </row>
-    <row r="143" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B143" s="16" t="s">
         <v>66</v>
       </c>
@@ -8240,7 +8240,7 @@
       <c r="O143" s="17"/>
       <c r="P143" s="18"/>
     </row>
-    <row r="144" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B144" s="16" t="s">
         <v>66</v>
       </c>
@@ -8261,7 +8261,7 @@
       <c r="O144" s="17"/>
       <c r="P144" s="18"/>
     </row>
-    <row r="145" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B145" s="16" t="s">
         <v>66</v>
       </c>
@@ -8282,7 +8282,7 @@
       <c r="O145" s="17"/>
       <c r="P145" s="18"/>
     </row>
-    <row r="146" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B146" s="16" t="s">
         <v>66</v>
       </c>
@@ -8303,7 +8303,7 @@
       <c r="O146" s="17"/>
       <c r="P146" s="18"/>
     </row>
-    <row r="147" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B147" s="16" t="s">
         <v>67</v>
       </c>
@@ -8324,7 +8324,7 @@
       <c r="O147" s="17"/>
       <c r="P147" s="18"/>
     </row>
-    <row r="148" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B148" s="16" t="s">
         <v>67</v>
       </c>
@@ -8345,7 +8345,7 @@
       <c r="O148" s="17"/>
       <c r="P148" s="18"/>
     </row>
-    <row r="149" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B149" s="16" t="s">
         <v>67</v>
       </c>
@@ -8366,7 +8366,7 @@
       <c r="O149" s="17"/>
       <c r="P149" s="18"/>
     </row>
-    <row r="150" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B150" s="16" t="s">
         <v>67</v>
       </c>
@@ -8387,7 +8387,7 @@
       <c r="O150" s="17"/>
       <c r="P150" s="18"/>
     </row>
-    <row r="151" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B151" s="16" t="s">
         <v>68</v>
       </c>
@@ -8408,7 +8408,7 @@
       <c r="O151" s="17"/>
       <c r="P151" s="18"/>
     </row>
-    <row r="152" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B152" s="16" t="s">
         <v>68</v>
       </c>
@@ -8429,7 +8429,7 @@
       <c r="O152" s="17"/>
       <c r="P152" s="18"/>
     </row>
-    <row r="153" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B153" s="16" t="s">
         <v>68</v>
       </c>
@@ -8450,7 +8450,7 @@
       <c r="O153" s="17"/>
       <c r="P153" s="18"/>
     </row>
-    <row r="154" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="16" t="s">
         <v>68</v>
       </c>
@@ -8471,7 +8471,7 @@
       <c r="O154" s="17"/>
       <c r="P154" s="18"/>
     </row>
-    <row r="155" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B155" s="16" t="s">
         <v>69</v>
       </c>
@@ -8492,7 +8492,7 @@
       <c r="O155" s="17"/>
       <c r="P155" s="18"/>
     </row>
-    <row r="156" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B156" s="16" t="s">
         <v>69</v>
       </c>
@@ -8513,7 +8513,7 @@
       <c r="O156" s="17"/>
       <c r="P156" s="18"/>
     </row>
-    <row r="157" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B157" s="16" t="s">
         <v>69</v>
       </c>
@@ -8534,7 +8534,7 @@
       <c r="O157" s="17"/>
       <c r="P157" s="18"/>
     </row>
-    <row r="158" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B158" s="16" t="s">
         <v>69</v>
       </c>
@@ -8555,7 +8555,7 @@
       <c r="O158" s="17"/>
       <c r="P158" s="18"/>
     </row>
-    <row r="159" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B159" s="16" t="s">
         <v>70</v>
       </c>
@@ -8576,7 +8576,7 @@
       <c r="O159" s="17"/>
       <c r="P159" s="18"/>
     </row>
-    <row r="160" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B160" s="16" t="s">
         <v>70</v>
       </c>
@@ -8597,7 +8597,7 @@
       <c r="O160" s="17"/>
       <c r="P160" s="18"/>
     </row>
-    <row r="161" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B161" s="16" t="s">
         <v>70</v>
       </c>
@@ -8618,7 +8618,7 @@
       <c r="O161" s="17"/>
       <c r="P161" s="18"/>
     </row>
-    <row r="162" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B162" s="16" t="s">
         <v>70</v>
       </c>
@@ -8639,7 +8639,7 @@
       <c r="O162" s="17"/>
       <c r="P162" s="18"/>
     </row>
-    <row r="163" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B163" s="16" t="s">
         <v>71</v>
       </c>
@@ -8660,7 +8660,7 @@
       <c r="O163" s="17"/>
       <c r="P163" s="18"/>
     </row>
-    <row r="164" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B164" s="16" t="s">
         <v>71</v>
       </c>
@@ -8681,7 +8681,7 @@
       <c r="O164" s="17"/>
       <c r="P164" s="18"/>
     </row>
-    <row r="165" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B165" s="16" t="s">
         <v>71</v>
       </c>
@@ -8702,7 +8702,7 @@
       <c r="O165" s="17"/>
       <c r="P165" s="18"/>
     </row>
-    <row r="166" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B166" s="16" t="s">
         <v>71</v>
       </c>
@@ -8723,7 +8723,7 @@
       <c r="O166" s="17"/>
       <c r="P166" s="18"/>
     </row>
-    <row r="167" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="16" t="s">
         <v>72</v>
       </c>
@@ -8744,7 +8744,7 @@
       <c r="O167" s="17"/>
       <c r="P167" s="18"/>
     </row>
-    <row r="168" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="16" t="s">
         <v>72</v>
       </c>
@@ -8765,7 +8765,7 @@
       <c r="O168" s="17"/>
       <c r="P168" s="18"/>
     </row>
-    <row r="169" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B169" s="16" t="s">
         <v>72</v>
       </c>
@@ -8786,7 +8786,7 @@
       <c r="O169" s="17"/>
       <c r="P169" s="18"/>
     </row>
-    <row r="170" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B170" s="16" t="s">
         <v>72</v>
       </c>
@@ -8807,7 +8807,7 @@
       <c r="O170" s="17"/>
       <c r="P170" s="18"/>
     </row>
-    <row r="171" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B171" s="16" t="s">
         <v>73</v>
       </c>
@@ -8828,7 +8828,7 @@
       <c r="O171" s="17"/>
       <c r="P171" s="18"/>
     </row>
-    <row r="172" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B172" s="16" t="s">
         <v>73</v>
       </c>
@@ -8849,7 +8849,7 @@
       <c r="O172" s="17"/>
       <c r="P172" s="18"/>
     </row>
-    <row r="173" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B173" s="16" t="s">
         <v>73</v>
       </c>
@@ -8870,7 +8870,7 @@
       <c r="O173" s="17"/>
       <c r="P173" s="18"/>
     </row>
-    <row r="174" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B174" s="16" t="s">
         <v>73</v>
       </c>
@@ -8891,7 +8891,7 @@
       <c r="O174" s="17"/>
       <c r="P174" s="18"/>
     </row>
-    <row r="175" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B175" s="16" t="s">
         <v>74</v>
       </c>
@@ -8912,7 +8912,7 @@
       <c r="O175" s="17"/>
       <c r="P175" s="18"/>
     </row>
-    <row r="176" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B176" s="16" t="s">
         <v>74</v>
       </c>
@@ -8933,7 +8933,7 @@
       <c r="O176" s="17"/>
       <c r="P176" s="18"/>
     </row>
-    <row r="177" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B177" s="16" t="s">
         <v>74</v>
       </c>
@@ -8954,7 +8954,7 @@
       <c r="O177" s="17"/>
       <c r="P177" s="18"/>
     </row>
-    <row r="178" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B178" s="16" t="s">
         <v>74</v>
       </c>
@@ -8975,7 +8975,7 @@
       <c r="O178" s="17"/>
       <c r="P178" s="18"/>
     </row>
-    <row r="179" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B179" s="16" t="s">
         <v>75</v>
       </c>
@@ -8996,7 +8996,7 @@
       <c r="O179" s="17"/>
       <c r="P179" s="18"/>
     </row>
-    <row r="180" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B180" s="16" t="s">
         <v>75</v>
       </c>
@@ -9017,7 +9017,7 @@
       <c r="O180" s="17"/>
       <c r="P180" s="18"/>
     </row>
-    <row r="181" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B181" s="16" t="s">
         <v>75</v>
       </c>
@@ -9038,7 +9038,7 @@
       <c r="O181" s="17"/>
       <c r="P181" s="18"/>
     </row>
-    <row r="182" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B182" s="16" t="s">
         <v>75</v>
       </c>
@@ -9059,7 +9059,7 @@
       <c r="O182" s="17"/>
       <c r="P182" s="18"/>
     </row>
-    <row r="183" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B183" s="16" t="s">
         <v>76</v>
       </c>
@@ -9080,7 +9080,7 @@
       <c r="O183" s="17"/>
       <c r="P183" s="18"/>
     </row>
-    <row r="184" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B184" s="16" t="s">
         <v>76</v>
       </c>
@@ -9101,7 +9101,7 @@
       <c r="O184" s="17"/>
       <c r="P184" s="18"/>
     </row>
-    <row r="185" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B185" s="16" t="s">
         <v>76</v>
       </c>
@@ -9122,7 +9122,7 @@
       <c r="O185" s="17"/>
       <c r="P185" s="18"/>
     </row>
-    <row r="186" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="186" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B186" s="16" t="s">
         <v>76</v>
       </c>
@@ -9143,7 +9143,7 @@
       <c r="O186" s="17"/>
       <c r="P186" s="18"/>
     </row>
-    <row r="187" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B187" s="16" t="s">
         <v>77</v>
       </c>
@@ -9164,7 +9164,7 @@
       <c r="O187" s="17"/>
       <c r="P187" s="18"/>
     </row>
-    <row r="188" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B188" s="16" t="s">
         <v>77</v>
       </c>
@@ -9185,7 +9185,7 @@
       <c r="O188" s="17"/>
       <c r="P188" s="18"/>
     </row>
-    <row r="189" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B189" s="16" t="s">
         <v>77</v>
       </c>
@@ -9206,7 +9206,7 @@
       <c r="O189" s="17"/>
       <c r="P189" s="18"/>
     </row>
-    <row r="190" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B190" s="16" t="s">
         <v>77</v>
       </c>
@@ -9227,7 +9227,7 @@
       <c r="O190" s="17"/>
       <c r="P190" s="18"/>
     </row>
-    <row r="191" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B191" s="16" t="s">
         <v>78</v>
       </c>
@@ -9248,7 +9248,7 @@
       <c r="O191" s="17"/>
       <c r="P191" s="18"/>
     </row>
-    <row r="192" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B192" s="16" t="s">
         <v>78</v>
       </c>
@@ -9269,7 +9269,7 @@
       <c r="O192" s="17"/>
       <c r="P192" s="18"/>
     </row>
-    <row r="193" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B193" s="16" t="s">
         <v>78</v>
       </c>
@@ -9290,7 +9290,7 @@
       <c r="O193" s="17"/>
       <c r="P193" s="18"/>
     </row>
-    <row r="194" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B194" s="16" t="s">
         <v>78</v>
       </c>
@@ -9311,7 +9311,7 @@
       <c r="O194" s="17"/>
       <c r="P194" s="18"/>
     </row>
-    <row r="195" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B195" s="16" t="s">
         <v>79</v>
       </c>
@@ -9332,7 +9332,7 @@
       <c r="O195" s="17"/>
       <c r="P195" s="18"/>
     </row>
-    <row r="196" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B196" s="16" t="s">
         <v>79</v>
       </c>
@@ -9353,7 +9353,7 @@
       <c r="O196" s="17"/>
       <c r="P196" s="18"/>
     </row>
-    <row r="197" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B197" s="16" t="s">
         <v>79</v>
       </c>
@@ -9374,7 +9374,7 @@
       <c r="O197" s="17"/>
       <c r="P197" s="18"/>
     </row>
-    <row r="198" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B198" s="16" t="s">
         <v>79</v>
       </c>
@@ -9395,7 +9395,7 @@
       <c r="O198" s="17"/>
       <c r="P198" s="18"/>
     </row>
-    <row r="199" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B199" s="16" t="s">
         <v>80</v>
       </c>
@@ -9416,7 +9416,7 @@
       <c r="O199" s="17"/>
       <c r="P199" s="18"/>
     </row>
-    <row r="200" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B200" s="16" t="s">
         <v>80</v>
       </c>
@@ -9437,7 +9437,7 @@
       <c r="O200" s="17"/>
       <c r="P200" s="18"/>
     </row>
-    <row r="201" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B201" s="16" t="s">
         <v>80</v>
       </c>
@@ -9458,7 +9458,7 @@
       <c r="O201" s="17"/>
       <c r="P201" s="18"/>
     </row>
-    <row r="202" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B202" s="16" t="s">
         <v>80</v>
       </c>
@@ -9479,7 +9479,7 @@
       <c r="O202" s="17"/>
       <c r="P202" s="18"/>
     </row>
-    <row r="203" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B203" s="16" t="s">
         <v>81</v>
       </c>
@@ -9500,7 +9500,7 @@
       <c r="O203" s="17"/>
       <c r="P203" s="18"/>
     </row>
-    <row r="204" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B204" s="16" t="s">
         <v>81</v>
       </c>
@@ -9521,7 +9521,7 @@
       <c r="O204" s="17"/>
       <c r="P204" s="18"/>
     </row>
-    <row r="205" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B205" s="16" t="s">
         <v>81</v>
       </c>
@@ -9542,7 +9542,7 @@
       <c r="O205" s="17"/>
       <c r="P205" s="18"/>
     </row>
-    <row r="206" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B206" s="16" t="s">
         <v>81</v>
       </c>
@@ -9563,7 +9563,7 @@
       <c r="O206" s="17"/>
       <c r="P206" s="18"/>
     </row>
-    <row r="207" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B207" s="16" t="s">
         <v>82</v>
       </c>
@@ -9584,7 +9584,7 @@
       <c r="O207" s="17"/>
       <c r="P207" s="18"/>
     </row>
-    <row r="208" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B208" s="16" t="s">
         <v>82</v>
       </c>
@@ -9605,7 +9605,7 @@
       <c r="O208" s="17"/>
       <c r="P208" s="18"/>
     </row>
-    <row r="209" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B209" s="16" t="s">
         <v>82</v>
       </c>
@@ -9626,7 +9626,7 @@
       <c r="O209" s="17"/>
       <c r="P209" s="18"/>
     </row>
-    <row r="210" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B210" s="16" t="s">
         <v>82</v>
       </c>
@@ -9647,7 +9647,7 @@
       <c r="O210" s="17"/>
       <c r="P210" s="18"/>
     </row>
-    <row r="211" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B211" s="16" t="s">
         <v>83</v>
       </c>
@@ -9668,7 +9668,7 @@
       <c r="O211" s="17"/>
       <c r="P211" s="18"/>
     </row>
-    <row r="212" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B212" s="16" t="s">
         <v>83</v>
       </c>
@@ -9689,7 +9689,7 @@
       <c r="O212" s="17"/>
       <c r="P212" s="18"/>
     </row>
-    <row r="213" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B213" s="16" t="s">
         <v>83</v>
       </c>
@@ -9710,7 +9710,7 @@
       <c r="O213" s="17"/>
       <c r="P213" s="18"/>
     </row>
-    <row r="214" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B214" s="16" t="s">
         <v>83</v>
       </c>
@@ -9731,7 +9731,7 @@
       <c r="O214" s="17"/>
       <c r="P214" s="18"/>
     </row>
-    <row r="215" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B215" s="16" t="s">
         <v>84</v>
       </c>
@@ -9752,7 +9752,7 @@
       <c r="O215" s="17"/>
       <c r="P215" s="18"/>
     </row>
-    <row r="216" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B216" s="16" t="s">
         <v>84</v>
       </c>
@@ -9773,7 +9773,7 @@
       <c r="O216" s="17"/>
       <c r="P216" s="18"/>
     </row>
-    <row r="217" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B217" s="16" t="s">
         <v>84</v>
       </c>
@@ -9794,7 +9794,7 @@
       <c r="O217" s="17"/>
       <c r="P217" s="18"/>
     </row>
-    <row r="218" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B218" s="16" t="s">
         <v>84</v>
       </c>
@@ -9815,7 +9815,7 @@
       <c r="O218" s="17"/>
       <c r="P218" s="18"/>
     </row>
-    <row r="219" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B219" s="16" t="s">
         <v>85</v>
       </c>
@@ -9836,7 +9836,7 @@
       <c r="O219" s="17"/>
       <c r="P219" s="18"/>
     </row>
-    <row r="220" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B220" s="16" t="s">
         <v>85</v>
       </c>
@@ -9857,7 +9857,7 @@
       <c r="O220" s="17"/>
       <c r="P220" s="18"/>
     </row>
-    <row r="221" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B221" s="16" t="s">
         <v>85</v>
       </c>
@@ -9878,7 +9878,7 @@
       <c r="O221" s="17"/>
       <c r="P221" s="18"/>
     </row>
-    <row r="222" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B222" s="16" t="s">
         <v>85</v>
       </c>
@@ -9899,7 +9899,7 @@
       <c r="O222" s="17"/>
       <c r="P222" s="18"/>
     </row>
-    <row r="223" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B223" s="16" t="s">
         <v>86</v>
       </c>
@@ -9920,7 +9920,7 @@
       <c r="O223" s="17"/>
       <c r="P223" s="18"/>
     </row>
-    <row r="224" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B224" s="16" t="s">
         <v>86</v>
       </c>
@@ -9941,7 +9941,7 @@
       <c r="O224" s="17"/>
       <c r="P224" s="18"/>
     </row>
-    <row r="225" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B225" s="16" t="s">
         <v>86</v>
       </c>
@@ -9962,7 +9962,7 @@
       <c r="O225" s="17"/>
       <c r="P225" s="18"/>
     </row>
-    <row r="226" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B226" s="16" t="s">
         <v>86</v>
       </c>
@@ -9983,7 +9983,7 @@
       <c r="O226" s="17"/>
       <c r="P226" s="18"/>
     </row>
-    <row r="227" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B227" s="16" t="s">
         <v>87</v>
       </c>
@@ -10004,7 +10004,7 @@
       <c r="O227" s="17"/>
       <c r="P227" s="18"/>
     </row>
-    <row r="228" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B228" s="16" t="s">
         <v>87</v>
       </c>
@@ -10025,7 +10025,7 @@
       <c r="O228" s="17"/>
       <c r="P228" s="18"/>
     </row>
-    <row r="229" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B229" s="16" t="s">
         <v>87</v>
       </c>
@@ -10046,7 +10046,7 @@
       <c r="O229" s="17"/>
       <c r="P229" s="18"/>
     </row>
-    <row r="230" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B230" s="16" t="s">
         <v>87</v>
       </c>
@@ -10067,7 +10067,7 @@
       <c r="O230" s="17"/>
       <c r="P230" s="18"/>
     </row>
-    <row r="231" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B231" s="16" t="s">
         <v>88</v>
       </c>
@@ -10088,7 +10088,7 @@
       <c r="O231" s="17"/>
       <c r="P231" s="18"/>
     </row>
-    <row r="232" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B232" s="16" t="s">
         <v>88</v>
       </c>
@@ -10109,7 +10109,7 @@
       <c r="O232" s="17"/>
       <c r="P232" s="18"/>
     </row>
-    <row r="233" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B233" s="16" t="s">
         <v>88</v>
       </c>
@@ -10130,7 +10130,7 @@
       <c r="O233" s="17"/>
       <c r="P233" s="18"/>
     </row>
-    <row r="234" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B234" s="16" t="s">
         <v>88</v>
       </c>
@@ -10151,7 +10151,7 @@
       <c r="O234" s="17"/>
       <c r="P234" s="18"/>
     </row>
-    <row r="235" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B235" s="16" t="s">
         <v>89</v>
       </c>
@@ -10172,7 +10172,7 @@
       <c r="O235" s="17"/>
       <c r="P235" s="18"/>
     </row>
-    <row r="236" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B236" s="16" t="s">
         <v>89</v>
       </c>
@@ -10193,7 +10193,7 @@
       <c r="O236" s="17"/>
       <c r="P236" s="18"/>
     </row>
-    <row r="237" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B237" s="16" t="s">
         <v>89</v>
       </c>
@@ -10214,7 +10214,7 @@
       <c r="O237" s="17"/>
       <c r="P237" s="18"/>
     </row>
-    <row r="238" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B238" s="16" t="s">
         <v>89</v>
       </c>
@@ -10235,7 +10235,7 @@
       <c r="O238" s="17"/>
       <c r="P238" s="18"/>
     </row>
-    <row r="239" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B239" s="16" t="s">
         <v>90</v>
       </c>
@@ -10256,7 +10256,7 @@
       <c r="O239" s="17"/>
       <c r="P239" s="18"/>
     </row>
-    <row r="240" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B240" s="16" t="s">
         <v>90</v>
       </c>
@@ -10277,7 +10277,7 @@
       <c r="O240" s="17"/>
       <c r="P240" s="18"/>
     </row>
-    <row r="241" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B241" s="16" t="s">
         <v>90</v>
       </c>
@@ -10298,7 +10298,7 @@
       <c r="O241" s="17"/>
       <c r="P241" s="18"/>
     </row>
-    <row r="242" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B242" s="16" t="s">
         <v>90</v>
       </c>
@@ -10319,7 +10319,7 @@
       <c r="O242" s="17"/>
       <c r="P242" s="18"/>
     </row>
-    <row r="243" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B243" s="16" t="s">
         <v>91</v>
       </c>
@@ -10340,7 +10340,7 @@
       <c r="O243" s="17"/>
       <c r="P243" s="18"/>
     </row>
-    <row r="244" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B244" s="16" t="s">
         <v>91</v>
       </c>
@@ -10361,7 +10361,7 @@
       <c r="O244" s="17"/>
       <c r="P244" s="18"/>
     </row>
-    <row r="245" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B245" s="16" t="s">
         <v>91</v>
       </c>
@@ -10382,7 +10382,7 @@
       <c r="O245" s="17"/>
       <c r="P245" s="18"/>
     </row>
-    <row r="246" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B246" s="16" t="s">
         <v>91</v>
       </c>
@@ -10403,7 +10403,7 @@
       <c r="O246" s="17"/>
       <c r="P246" s="18"/>
     </row>
-    <row r="247" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B247" s="16" t="s">
         <v>92</v>
       </c>
@@ -10424,7 +10424,7 @@
       <c r="O247" s="17"/>
       <c r="P247" s="18"/>
     </row>
-    <row r="248" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B248" s="16" t="s">
         <v>92</v>
       </c>
@@ -10445,7 +10445,7 @@
       <c r="O248" s="17"/>
       <c r="P248" s="18"/>
     </row>
-    <row r="249" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B249" s="16" t="s">
         <v>92</v>
       </c>
@@ -10466,7 +10466,7 @@
       <c r="O249" s="17"/>
       <c r="P249" s="18"/>
     </row>
-    <row r="250" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B250" s="16" t="s">
         <v>92</v>
       </c>
@@ -10487,7 +10487,7 @@
       <c r="O250" s="17"/>
       <c r="P250" s="18"/>
     </row>
-    <row r="251" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B251" s="16" t="s">
         <v>93</v>
       </c>
@@ -10508,7 +10508,7 @@
       <c r="O251" s="17"/>
       <c r="P251" s="18"/>
     </row>
-    <row r="252" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B252" s="16" t="s">
         <v>93</v>
       </c>
@@ -10529,7 +10529,7 @@
       <c r="O252" s="17"/>
       <c r="P252" s="18"/>
     </row>
-    <row r="253" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B253" s="16" t="s">
         <v>93</v>
       </c>
@@ -10550,7 +10550,7 @@
       <c r="O253" s="17"/>
       <c r="P253" s="18"/>
     </row>
-    <row r="254" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B254" s="16" t="s">
         <v>93</v>
       </c>
@@ -10571,7 +10571,7 @@
       <c r="O254" s="17"/>
       <c r="P254" s="18"/>
     </row>
-    <row r="255" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B255" s="16" t="s">
         <v>94</v>
       </c>
@@ -10592,7 +10592,7 @@
       <c r="O255" s="17"/>
       <c r="P255" s="18"/>
     </row>
-    <row r="256" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B256" s="16" t="s">
         <v>94</v>
       </c>
@@ -10613,7 +10613,7 @@
       <c r="O256" s="17"/>
       <c r="P256" s="18"/>
     </row>
-    <row r="257" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B257" s="16" t="s">
         <v>94</v>
       </c>
@@ -10634,7 +10634,7 @@
       <c r="O257" s="17"/>
       <c r="P257" s="18"/>
     </row>
-    <row r="258" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B258" s="16" t="s">
         <v>94</v>
       </c>
@@ -10655,7 +10655,7 @@
       <c r="O258" s="17"/>
       <c r="P258" s="18"/>
     </row>
-    <row r="259" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B259" s="16" t="s">
         <v>95</v>
       </c>
@@ -10676,7 +10676,7 @@
       <c r="O259" s="17"/>
       <c r="P259" s="18"/>
     </row>
-    <row r="260" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B260" s="16" t="s">
         <v>95</v>
       </c>
@@ -10697,7 +10697,7 @@
       <c r="O260" s="17"/>
       <c r="P260" s="18"/>
     </row>
-    <row r="261" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B261" s="16" t="s">
         <v>95</v>
       </c>
@@ -10718,7 +10718,7 @@
       <c r="O261" s="17"/>
       <c r="P261" s="18"/>
     </row>
-    <row r="262" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B262" s="16" t="s">
         <v>95</v>
       </c>
@@ -10739,7 +10739,7 @@
       <c r="O262" s="17"/>
       <c r="P262" s="18"/>
     </row>
-    <row r="263" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B263" s="16" t="s">
         <v>96</v>
       </c>
@@ -10760,7 +10760,7 @@
       <c r="O263" s="17"/>
       <c r="P263" s="18"/>
     </row>
-    <row r="264" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B264" s="16" t="s">
         <v>96</v>
       </c>
@@ -10781,7 +10781,7 @@
       <c r="O264" s="17"/>
       <c r="P264" s="18"/>
     </row>
-    <row r="265" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B265" s="16" t="s">
         <v>96</v>
       </c>
@@ -10802,7 +10802,7 @@
       <c r="O265" s="17"/>
       <c r="P265" s="18"/>
     </row>
-    <row r="266" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B266" s="16" t="s">
         <v>97</v>
       </c>
@@ -10823,7 +10823,7 @@
       <c r="O266" s="17"/>
       <c r="P266" s="18"/>
     </row>
-    <row r="267" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B267" s="16" t="s">
         <v>97</v>
       </c>
@@ -10844,7 +10844,7 @@
       <c r="O267" s="17"/>
       <c r="P267" s="18"/>
     </row>
-    <row r="268" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B268" s="16" t="s">
         <v>97</v>
       </c>
@@ -10865,7 +10865,7 @@
       <c r="O268" s="17"/>
       <c r="P268" s="18"/>
     </row>
-    <row r="269" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B269" s="16" t="s">
         <v>97</v>
       </c>
@@ -10886,7 +10886,7 @@
       <c r="O269" s="17"/>
       <c r="P269" s="18"/>
     </row>
-    <row r="270" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B270" s="16" t="s">
         <v>98</v>
       </c>
@@ -10907,7 +10907,7 @@
       <c r="O270" s="17"/>
       <c r="P270" s="18"/>
     </row>
-    <row r="271" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B271" s="16" t="s">
         <v>98</v>
       </c>
@@ -10928,7 +10928,7 @@
       <c r="O271" s="17"/>
       <c r="P271" s="18"/>
     </row>
-    <row r="272" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B272" s="16" t="s">
         <v>98</v>
       </c>
@@ -10949,7 +10949,7 @@
       <c r="O272" s="17"/>
       <c r="P272" s="18"/>
     </row>
-    <row r="273" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B273" s="16" t="s">
         <v>98</v>
       </c>
@@ -10970,7 +10970,7 @@
       <c r="O273" s="17"/>
       <c r="P273" s="18"/>
     </row>
-    <row r="274" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B274" s="16" t="s">
         <v>99</v>
       </c>
@@ -10991,7 +10991,7 @@
       <c r="O274" s="17"/>
       <c r="P274" s="18"/>
     </row>
-    <row r="275" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B275" s="16" t="s">
         <v>99</v>
       </c>
@@ -11012,7 +11012,7 @@
       <c r="O275" s="17"/>
       <c r="P275" s="18"/>
     </row>
-    <row r="276" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B276" s="16" t="s">
         <v>99</v>
       </c>
@@ -11033,7 +11033,7 @@
       <c r="O276" s="17"/>
       <c r="P276" s="18"/>
     </row>
-    <row r="277" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B277" s="16" t="s">
         <v>99</v>
       </c>
@@ -11054,7 +11054,7 @@
       <c r="O277" s="17"/>
       <c r="P277" s="18"/>
     </row>
-    <row r="278" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B278" s="16" t="s">
         <v>100</v>
       </c>
@@ -11075,7 +11075,7 @@
       <c r="O278" s="17"/>
       <c r="P278" s="18"/>
     </row>
-    <row r="279" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B279" s="16" t="s">
         <v>100</v>
       </c>
@@ -11096,7 +11096,7 @@
       <c r="O279" s="17"/>
       <c r="P279" s="18"/>
     </row>
-    <row r="280" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B280" s="16" t="s">
         <v>100</v>
       </c>
@@ -11117,7 +11117,7 @@
       <c r="O280" s="17"/>
       <c r="P280" s="18"/>
     </row>
-    <row r="281" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B281" s="16" t="s">
         <v>100</v>
       </c>
@@ -11138,7 +11138,7 @@
       <c r="O281" s="17"/>
       <c r="P281" s="18"/>
     </row>
-    <row r="282" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B282" s="16" t="s">
         <v>101</v>
       </c>
@@ -11159,7 +11159,7 @@
       <c r="O282" s="17"/>
       <c r="P282" s="18"/>
     </row>
-    <row r="283" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B283" s="16" t="s">
         <v>101</v>
       </c>
@@ -11180,7 +11180,7 @@
       <c r="O283" s="17"/>
       <c r="P283" s="18"/>
     </row>
-    <row r="284" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B284" s="16" t="s">
         <v>101</v>
       </c>
@@ -11201,7 +11201,7 @@
       <c r="O284" s="17"/>
       <c r="P284" s="18"/>
     </row>
-    <row r="285" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B285" s="16" t="s">
         <v>101</v>
       </c>
@@ -11222,7 +11222,7 @@
       <c r="O285" s="17"/>
       <c r="P285" s="18"/>
     </row>
-    <row r="286" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B286" s="16" t="s">
         <v>102</v>
       </c>
@@ -11243,7 +11243,7 @@
       <c r="O286" s="17"/>
       <c r="P286" s="18"/>
     </row>
-    <row r="287" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B287" s="16" t="s">
         <v>102</v>
       </c>
@@ -11264,7 +11264,7 @@
       <c r="O287" s="17"/>
       <c r="P287" s="18"/>
     </row>
-    <row r="288" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B288" s="16" t="s">
         <v>102</v>
       </c>
@@ -11285,7 +11285,7 @@
       <c r="O288" s="17"/>
       <c r="P288" s="18"/>
     </row>
-    <row r="289" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B289" s="16" t="s">
         <v>31</v>
       </c>
@@ -11306,7 +11306,7 @@
       <c r="O289" s="17"/>
       <c r="P289" s="18"/>
     </row>
-    <row r="290" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B290" s="16" t="s">
         <v>31</v>
       </c>
@@ -11327,7 +11327,7 @@
       <c r="O290" s="17"/>
       <c r="P290" s="18"/>
     </row>
-    <row r="291" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B291" s="16" t="s">
         <v>31</v>
       </c>
@@ -11348,7 +11348,7 @@
       <c r="O291" s="17"/>
       <c r="P291" s="18"/>
     </row>
-    <row r="292" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B292" s="16" t="s">
         <v>31</v>
       </c>
@@ -11369,7 +11369,7 @@
       <c r="O292" s="17"/>
       <c r="P292" s="18"/>
     </row>
-    <row r="293" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B293" s="16" t="s">
         <v>103</v>
       </c>
@@ -11390,7 +11390,7 @@
       <c r="O293" s="17"/>
       <c r="P293" s="18"/>
     </row>
-    <row r="294" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B294" s="16" t="s">
         <v>103</v>
       </c>
@@ -11411,7 +11411,7 @@
       <c r="O294" s="17"/>
       <c r="P294" s="18"/>
     </row>
-    <row r="295" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B295" s="16" t="s">
         <v>103</v>
       </c>
@@ -11432,7 +11432,7 @@
       <c r="O295" s="17"/>
       <c r="P295" s="18"/>
     </row>
-    <row r="296" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B296" s="16" t="s">
         <v>104</v>
       </c>
@@ -11453,7 +11453,7 @@
       <c r="O296" s="17"/>
       <c r="P296" s="18"/>
     </row>
-    <row r="297" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B297" s="16" t="s">
         <v>104</v>
       </c>
@@ -11474,7 +11474,7 @@
       <c r="O297" s="17"/>
       <c r="P297" s="18"/>
     </row>
-    <row r="298" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B298" s="16" t="s">
         <v>104</v>
       </c>
@@ -11495,7 +11495,7 @@
       <c r="O298" s="17"/>
       <c r="P298" s="18"/>
     </row>
-    <row r="299" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B299" s="16" t="s">
         <v>105</v>
       </c>
@@ -11516,7 +11516,7 @@
       <c r="O299" s="17"/>
       <c r="P299" s="18"/>
     </row>
-    <row r="300" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B300" s="16" t="s">
         <v>105</v>
       </c>
@@ -11537,7 +11537,7 @@
       <c r="O300" s="17"/>
       <c r="P300" s="18"/>
     </row>
-    <row r="301" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B301" s="16" t="s">
         <v>105</v>
       </c>
@@ -11558,7 +11558,7 @@
       <c r="O301" s="17"/>
       <c r="P301" s="18"/>
     </row>
-    <row r="302" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B302" s="16" t="s">
         <v>105</v>
       </c>
@@ -11579,7 +11579,7 @@
       <c r="O302" s="17"/>
       <c r="P302" s="18"/>
     </row>
-    <row r="303" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B303" s="16" t="s">
         <v>106</v>
       </c>
@@ -11600,7 +11600,7 @@
       <c r="O303" s="17"/>
       <c r="P303" s="18"/>
     </row>
-    <row r="304" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B304" s="16" t="s">
         <v>106</v>
       </c>
@@ -11621,7 +11621,7 @@
       <c r="O304" s="17"/>
       <c r="P304" s="18"/>
     </row>
-    <row r="305" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B305" s="16" t="s">
         <v>106</v>
       </c>
@@ -11642,7 +11642,7 @@
       <c r="O305" s="17"/>
       <c r="P305" s="18"/>
     </row>
-    <row r="306" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B306" s="16" t="s">
         <v>107</v>
       </c>
@@ -11663,7 +11663,7 @@
       <c r="O306" s="17"/>
       <c r="P306" s="18"/>
     </row>
-    <row r="307" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B307" s="16" t="s">
         <v>107</v>
       </c>
@@ -11684,7 +11684,7 @@
       <c r="O307" s="17"/>
       <c r="P307" s="18"/>
     </row>
-    <row r="308" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B308" s="16" t="s">
         <v>107</v>
       </c>
@@ -11705,7 +11705,7 @@
       <c r="O308" s="17"/>
       <c r="P308" s="18"/>
     </row>
-    <row r="309" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B309" s="16" t="s">
         <v>108</v>
       </c>
@@ -11726,7 +11726,7 @@
       <c r="O309" s="17"/>
       <c r="P309" s="18"/>
     </row>
-    <row r="310" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B310" s="16" t="s">
         <v>108</v>
       </c>
@@ -11747,7 +11747,7 @@
       <c r="O310" s="17"/>
       <c r="P310" s="18"/>
     </row>
-    <row r="311" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B311" s="16" t="s">
         <v>108</v>
       </c>
@@ -11768,7 +11768,7 @@
       <c r="O311" s="17"/>
       <c r="P311" s="18"/>
     </row>
-    <row r="312" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B312" s="16" t="s">
         <v>109</v>
       </c>
@@ -11789,7 +11789,7 @@
       <c r="O312" s="17"/>
       <c r="P312" s="18"/>
     </row>
-    <row r="313" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B313" s="16" t="s">
         <v>109</v>
       </c>
@@ -11810,7 +11810,7 @@
       <c r="O313" s="17"/>
       <c r="P313" s="18"/>
     </row>
-    <row r="314" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B314" s="16" t="s">
         <v>109</v>
       </c>
@@ -11831,7 +11831,7 @@
       <c r="O314" s="17"/>
       <c r="P314" s="18"/>
     </row>
-    <row r="315" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B315" s="16" t="s">
         <v>110</v>
       </c>
@@ -11852,7 +11852,7 @@
       <c r="O315" s="17"/>
       <c r="P315" s="18"/>
     </row>
-    <row r="316" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B316" s="16" t="s">
         <v>110</v>
       </c>
@@ -11873,7 +11873,7 @@
       <c r="O316" s="17"/>
       <c r="P316" s="18"/>
     </row>
-    <row r="317" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B317" s="16" t="s">
         <v>110</v>
       </c>
@@ -11894,7 +11894,7 @@
       <c r="O317" s="17"/>
       <c r="P317" s="18"/>
     </row>
-    <row r="318" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B318" s="16" t="s">
         <v>111</v>
       </c>
@@ -11915,7 +11915,7 @@
       <c r="O318" s="17"/>
       <c r="P318" s="18"/>
     </row>
-    <row r="319" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B319" s="16" t="s">
         <v>111</v>
       </c>
@@ -11936,7 +11936,7 @@
       <c r="O319" s="17"/>
       <c r="P319" s="18"/>
     </row>
-    <row r="320" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B320" s="16" t="s">
         <v>111</v>
       </c>
@@ -11957,7 +11957,7 @@
       <c r="O320" s="17"/>
       <c r="P320" s="18"/>
     </row>
-    <row r="321" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="321" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B321" s="16" t="s">
         <v>111</v>
       </c>
@@ -11978,7 +11978,7 @@
       <c r="O321" s="17"/>
       <c r="P321" s="18"/>
     </row>
-    <row r="322" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B322" s="16" t="s">
         <v>91</v>
       </c>
@@ -11999,7 +11999,7 @@
       <c r="O322" s="17"/>
       <c r="P322" s="18"/>
     </row>
-    <row r="323" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B323" s="16" t="s">
         <v>91</v>
       </c>
@@ -12020,7 +12020,7 @@
       <c r="O323" s="17"/>
       <c r="P323" s="18"/>
     </row>
-    <row r="324" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B324" s="16" t="s">
         <v>91</v>
       </c>
@@ -12041,7 +12041,7 @@
       <c r="O324" s="17"/>
       <c r="P324" s="18"/>
     </row>
-    <row r="325" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B325" s="16" t="s">
         <v>91</v>
       </c>
@@ -12062,7 +12062,7 @@
       <c r="O325" s="17"/>
       <c r="P325" s="18"/>
     </row>
-    <row r="326" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B326" s="16" t="s">
         <v>92</v>
       </c>
@@ -12083,7 +12083,7 @@
       <c r="O326" s="17"/>
       <c r="P326" s="18"/>
     </row>
-    <row r="327" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B327" s="16" t="s">
         <v>92</v>
       </c>
@@ -12104,7 +12104,7 @@
       <c r="O327" s="17"/>
       <c r="P327" s="18"/>
     </row>
-    <row r="328" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B328" s="16" t="s">
         <v>92</v>
       </c>
@@ -12125,7 +12125,7 @@
       <c r="O328" s="17"/>
       <c r="P328" s="18"/>
     </row>
-    <row r="329" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B329" s="16" t="s">
         <v>92</v>
       </c>
@@ -12146,7 +12146,7 @@
       <c r="O329" s="17"/>
       <c r="P329" s="18"/>
     </row>
-    <row r="330" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B330" s="16" t="s">
         <v>93</v>
       </c>
@@ -12167,7 +12167,7 @@
       <c r="O330" s="17"/>
       <c r="P330" s="18"/>
     </row>
-    <row r="331" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B331" s="16" t="s">
         <v>93</v>
       </c>
@@ -12188,7 +12188,7 @@
       <c r="O331" s="17"/>
       <c r="P331" s="18"/>
     </row>
-    <row r="332" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B332" s="16" t="s">
         <v>93</v>
       </c>
@@ -12209,7 +12209,7 @@
       <c r="O332" s="17"/>
       <c r="P332" s="18"/>
     </row>
-    <row r="333" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B333" s="16" t="s">
         <v>93</v>
       </c>
@@ -12230,7 +12230,7 @@
       <c r="O333" s="17"/>
       <c r="P333" s="18"/>
     </row>
-    <row r="334" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B334" s="16" t="s">
         <v>94</v>
       </c>
@@ -12251,7 +12251,7 @@
       <c r="O334" s="17"/>
       <c r="P334" s="18"/>
     </row>
-    <row r="335" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B335" s="16" t="s">
         <v>94</v>
       </c>
@@ -12272,7 +12272,7 @@
       <c r="O335" s="17"/>
       <c r="P335" s="18"/>
     </row>
-    <row r="336" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B336" s="16" t="s">
         <v>94</v>
       </c>
@@ -12293,7 +12293,7 @@
       <c r="O336" s="17"/>
       <c r="P336" s="18"/>
     </row>
-    <row r="337" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B337" s="16" t="s">
         <v>94</v>
       </c>
@@ -12314,7 +12314,7 @@
       <c r="O337" s="17"/>
       <c r="P337" s="18"/>
     </row>
-    <row r="338" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B338" s="16" t="s">
         <v>95</v>
       </c>
@@ -12335,7 +12335,7 @@
       <c r="O338" s="17"/>
       <c r="P338" s="18"/>
     </row>
-    <row r="339" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B339" s="16" t="s">
         <v>95</v>
       </c>
@@ -12356,7 +12356,7 @@
       <c r="O339" s="17"/>
       <c r="P339" s="18"/>
     </row>
-    <row r="340" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B340" s="16" t="s">
         <v>95</v>
       </c>
@@ -12377,7 +12377,7 @@
       <c r="O340" s="17"/>
       <c r="P340" s="18"/>
     </row>
-    <row r="341" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B341" s="16" t="s">
         <v>95</v>
       </c>
@@ -12398,7 +12398,7 @@
       <c r="O341" s="17"/>
       <c r="P341" s="18"/>
     </row>
-    <row r="342" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B342" s="16" t="s">
         <v>96</v>
       </c>
@@ -12419,7 +12419,7 @@
       <c r="O342" s="17"/>
       <c r="P342" s="18"/>
     </row>
-    <row r="343" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B343" s="16" t="s">
         <v>96</v>
       </c>
@@ -12440,7 +12440,7 @@
       <c r="O343" s="17"/>
       <c r="P343" s="18"/>
     </row>
-    <row r="344" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B344" s="16" t="s">
         <v>96</v>
       </c>
@@ -12461,7 +12461,7 @@
       <c r="O344" s="17"/>
       <c r="P344" s="18"/>
     </row>
-    <row r="345" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B345" s="16" t="s">
         <v>97</v>
       </c>
@@ -12482,7 +12482,7 @@
       <c r="O345" s="17"/>
       <c r="P345" s="18"/>
     </row>
-    <row r="346" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B346" s="16" t="s">
         <v>97</v>
       </c>
@@ -12503,7 +12503,7 @@
       <c r="O346" s="17"/>
       <c r="P346" s="18"/>
     </row>
-    <row r="347" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B347" s="16" t="s">
         <v>97</v>
       </c>
@@ -12524,7 +12524,7 @@
       <c r="O347" s="17"/>
       <c r="P347" s="18"/>
     </row>
-    <row r="348" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B348" s="16" t="s">
         <v>97</v>
       </c>
@@ -12545,7 +12545,7 @@
       <c r="O348" s="17"/>
       <c r="P348" s="18"/>
     </row>
-    <row r="349" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B349" s="16" t="s">
         <v>98</v>
       </c>
@@ -12566,7 +12566,7 @@
       <c r="O349" s="17"/>
       <c r="P349" s="18"/>
     </row>
-    <row r="350" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B350" s="16" t="s">
         <v>98</v>
       </c>
@@ -12587,7 +12587,7 @@
       <c r="O350" s="17"/>
       <c r="P350" s="18"/>
     </row>
-    <row r="351" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B351" s="16" t="s">
         <v>98</v>
       </c>
@@ -12608,7 +12608,7 @@
       <c r="O351" s="17"/>
       <c r="P351" s="18"/>
     </row>
-    <row r="352" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B352" s="16" t="s">
         <v>98</v>
       </c>
@@ -12629,7 +12629,7 @@
       <c r="O352" s="17"/>
       <c r="P352" s="18"/>
     </row>
-    <row r="353" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B353" s="16" t="s">
         <v>99</v>
       </c>
@@ -12650,7 +12650,7 @@
       <c r="O353" s="17"/>
       <c r="P353" s="18"/>
     </row>
-    <row r="354" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B354" s="16" t="s">
         <v>99</v>
       </c>
@@ -12671,7 +12671,7 @@
       <c r="O354" s="17"/>
       <c r="P354" s="18"/>
     </row>
-    <row r="355" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B355" s="16" t="s">
         <v>99</v>
       </c>
@@ -12692,7 +12692,7 @@
       <c r="O355" s="17"/>
       <c r="P355" s="18"/>
     </row>
-    <row r="356" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B356" s="16" t="s">
         <v>99</v>
       </c>
@@ -12713,7 +12713,7 @@
       <c r="O356" s="17"/>
       <c r="P356" s="18"/>
     </row>
-    <row r="357" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B357" s="16" t="s">
         <v>100</v>
       </c>
@@ -12734,7 +12734,7 @@
       <c r="O357" s="17"/>
       <c r="P357" s="18"/>
     </row>
-    <row r="358" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B358" s="16" t="s">
         <v>100</v>
       </c>
@@ -12755,7 +12755,7 @@
       <c r="O358" s="17"/>
       <c r="P358" s="18"/>
     </row>
-    <row r="359" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B359" s="16" t="s">
         <v>100</v>
       </c>
@@ -12776,7 +12776,7 @@
       <c r="O359" s="17"/>
       <c r="P359" s="18"/>
     </row>
-    <row r="360" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B360" s="16" t="s">
         <v>100</v>
       </c>
@@ -12797,7 +12797,7 @@
       <c r="O360" s="17"/>
       <c r="P360" s="18"/>
     </row>
-    <row r="361" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B361" s="16" t="s">
         <v>101</v>
       </c>
@@ -12818,7 +12818,7 @@
       <c r="O361" s="17"/>
       <c r="P361" s="18"/>
     </row>
-    <row r="362" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B362" s="16" t="s">
         <v>101</v>
       </c>
@@ -12839,7 +12839,7 @@
       <c r="O362" s="17"/>
       <c r="P362" s="18"/>
     </row>
-    <row r="363" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B363" s="16" t="s">
         <v>101</v>
       </c>
@@ -12860,7 +12860,7 @@
       <c r="O363" s="17"/>
       <c r="P363" s="18"/>
     </row>
-    <row r="364" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B364" s="16" t="s">
         <v>101</v>
       </c>
@@ -12881,7 +12881,7 @@
       <c r="O364" s="17"/>
       <c r="P364" s="18"/>
     </row>
-    <row r="365" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B365" s="16" t="s">
         <v>112</v>
       </c>
@@ -12902,7 +12902,7 @@
       <c r="O365" s="17"/>
       <c r="P365" s="18"/>
     </row>
-    <row r="366" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B366" s="16" t="s">
         <v>112</v>
       </c>
@@ -12923,7 +12923,7 @@
       <c r="O366" s="17"/>
       <c r="P366" s="18"/>
     </row>
-    <row r="367" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B367" s="16" t="s">
         <v>112</v>
       </c>
@@ -12944,7 +12944,7 @@
       <c r="O367" s="17"/>
       <c r="P367" s="18"/>
     </row>
-    <row r="368" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B368" s="16" t="s">
         <v>112</v>
       </c>
@@ -12965,7 +12965,7 @@
       <c r="O368" s="17"/>
       <c r="P368" s="18"/>
     </row>
-    <row r="369" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B369" s="16" t="s">
         <v>113</v>
       </c>
@@ -12986,7 +12986,7 @@
       <c r="O369" s="17"/>
       <c r="P369" s="18"/>
     </row>
-    <row r="370" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B370" s="16" t="s">
         <v>113</v>
       </c>
@@ -13007,7 +13007,7 @@
       <c r="O370" s="17"/>
       <c r="P370" s="18"/>
     </row>
-    <row r="371" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B371" s="16" t="s">
         <v>113</v>
       </c>
@@ -13028,7 +13028,7 @@
       <c r="O371" s="17"/>
       <c r="P371" s="18"/>
     </row>
-    <row r="372" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B372" s="16" t="s">
         <v>114</v>
       </c>
@@ -13049,7 +13049,7 @@
       <c r="O372" s="17"/>
       <c r="P372" s="18"/>
     </row>
-    <row r="373" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B373" s="16" t="s">
         <v>114</v>
       </c>
@@ -13070,7 +13070,7 @@
       <c r="O373" s="17"/>
       <c r="P373" s="18"/>
     </row>
-    <row r="374" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B374" s="16" t="s">
         <v>114</v>
       </c>
@@ -13091,7 +13091,7 @@
       <c r="O374" s="17"/>
       <c r="P374" s="18"/>
     </row>
-    <row r="375" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B375" s="16" t="s">
         <v>114</v>
       </c>
@@ -13112,7 +13112,7 @@
       <c r="O375" s="17"/>
       <c r="P375" s="18"/>
     </row>
-    <row r="376" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B376" s="16" t="s">
         <v>115</v>
       </c>
@@ -13133,7 +13133,7 @@
       <c r="O376" s="17"/>
       <c r="P376" s="18"/>
     </row>
-    <row r="377" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B377" s="16" t="s">
         <v>115</v>
       </c>
@@ -13154,7 +13154,7 @@
       <c r="O377" s="17"/>
       <c r="P377" s="18"/>
     </row>
-    <row r="378" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B378" s="16" t="s">
         <v>115</v>
       </c>
@@ -13175,7 +13175,7 @@
       <c r="O378" s="17"/>
       <c r="P378" s="18"/>
     </row>
-    <row r="379" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B379" s="16" t="s">
         <v>115</v>
       </c>
@@ -13196,7 +13196,7 @@
       <c r="O379" s="17"/>
       <c r="P379" s="18"/>
     </row>
-    <row r="380" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B380" s="16" t="s">
         <v>116</v>
       </c>
@@ -13217,7 +13217,7 @@
       <c r="O380" s="17"/>
       <c r="P380" s="18"/>
     </row>
-    <row r="381" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B381" s="16" t="s">
         <v>116</v>
       </c>
@@ -13238,7 +13238,7 @@
       <c r="O381" s="17"/>
       <c r="P381" s="18"/>
     </row>
-    <row r="382" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B382" s="16" t="s">
         <v>116</v>
       </c>
@@ -13259,7 +13259,7 @@
       <c r="O382" s="17"/>
       <c r="P382" s="18"/>
     </row>
-    <row r="383" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B383" s="16" t="s">
         <v>117</v>
       </c>
@@ -13280,7 +13280,7 @@
       <c r="O383" s="17"/>
       <c r="P383" s="18"/>
     </row>
-    <row r="384" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B384" s="16" t="s">
         <v>117</v>
       </c>
@@ -13301,7 +13301,7 @@
       <c r="O384" s="17"/>
       <c r="P384" s="18"/>
     </row>
-    <row r="385" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B385" s="16" t="s">
         <v>117</v>
       </c>
@@ -13322,7 +13322,7 @@
       <c r="O385" s="17"/>
       <c r="P385" s="18"/>
     </row>
-    <row r="386" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B386" s="16" t="s">
         <v>117</v>
       </c>
@@ -13343,7 +13343,7 @@
       <c r="O386" s="17"/>
       <c r="P386" s="18"/>
     </row>
-    <row r="387" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B387" s="16" t="s">
         <v>118</v>
       </c>
@@ -13364,7 +13364,7 @@
       <c r="O387" s="17"/>
       <c r="P387" s="18"/>
     </row>
-    <row r="388" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B388" s="16" t="s">
         <v>118</v>
       </c>
@@ -13385,7 +13385,7 @@
       <c r="O388" s="17"/>
       <c r="P388" s="18"/>
     </row>
-    <row r="389" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B389" s="16" t="s">
         <v>118</v>
       </c>
@@ -13406,7 +13406,7 @@
       <c r="O389" s="17"/>
       <c r="P389" s="18"/>
     </row>
-    <row r="390" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B390" s="16" t="s">
         <v>119</v>
       </c>
@@ -13427,7 +13427,7 @@
       <c r="O390" s="17"/>
       <c r="P390" s="18"/>
     </row>
-    <row r="391" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B391" s="16" t="s">
         <v>119</v>
       </c>
@@ -13448,7 +13448,7 @@
       <c r="O391" s="17"/>
       <c r="P391" s="18"/>
     </row>
-    <row r="392" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B392" s="16" t="s">
         <v>119</v>
       </c>
@@ -13469,7 +13469,7 @@
       <c r="O392" s="17"/>
       <c r="P392" s="18"/>
     </row>
-    <row r="393" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B393" s="16" t="s">
         <v>120</v>
       </c>
@@ -13490,7 +13490,7 @@
       <c r="O393" s="17"/>
       <c r="P393" s="18"/>
     </row>
-    <row r="394" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B394" s="16" t="s">
         <v>120</v>
       </c>
@@ -13511,7 +13511,7 @@
       <c r="O394" s="17"/>
       <c r="P394" s="18"/>
     </row>
-    <row r="395" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B395" s="16" t="s">
         <v>120</v>
       </c>
@@ -13532,7 +13532,7 @@
       <c r="O395" s="17"/>
       <c r="P395" s="18"/>
     </row>
-    <row r="396" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B396" s="16" t="s">
         <v>121</v>
       </c>
@@ -13553,7 +13553,7 @@
       <c r="O396" s="17"/>
       <c r="P396" s="18"/>
     </row>
-    <row r="397" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B397" s="16" t="s">
         <v>121</v>
       </c>
@@ -13574,7 +13574,7 @@
       <c r="O397" s="17"/>
       <c r="P397" s="18"/>
     </row>
-    <row r="398" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B398" s="16" t="s">
         <v>121</v>
       </c>
@@ -13595,7 +13595,7 @@
       <c r="O398" s="17"/>
       <c r="P398" s="18"/>
     </row>
-    <row r="399" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B399" s="25" t="s">
         <v>121</v>
       </c>
@@ -13628,36 +13628,36 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC6B4A01-2FBC-4D4D-87FA-D468B6989493}">
   <dimension ref="A1:P399"/>
-  <sheetFormatPr defaultColWidth="8.19921875" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.25" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="70" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="59" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.8984375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="32.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="37.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="8.19921875" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.19921875" style="1"/>
+    <col min="11" max="11" width="15.875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="32.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="37.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="8.25" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.25" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
@@ -13676,7 +13676,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" s="11" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" s="11" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -13688,7 +13688,7 @@
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
     </row>
-    <row r="4" spans="1:16" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="52.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="23" t="s">
         <v>0</v>
       </c>
@@ -13735,7 +13735,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12" t="s">
         <v>2</v>
       </c>
@@ -13756,7 +13756,7 @@
       <c r="O5" s="17"/>
       <c r="P5" s="35"/>
     </row>
-    <row r="6" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="16" t="s">
         <v>2</v>
       </c>
@@ -13777,7 +13777,7 @@
       <c r="O6" s="17"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
         <v>2</v>
       </c>
@@ -13798,7 +13798,7 @@
       <c r="O7" s="17"/>
       <c r="P7" s="18"/>
     </row>
-    <row r="8" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
         <v>2</v>
       </c>
@@ -13819,7 +13819,7 @@
       <c r="O8" s="17"/>
       <c r="P8" s="18"/>
     </row>
-    <row r="9" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
         <v>3</v>
       </c>
@@ -13840,7 +13840,7 @@
       <c r="O9" s="17"/>
       <c r="P9" s="18"/>
     </row>
-    <row r="10" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -13864,7 +13864,7 @@
       <c r="O10" s="17"/>
       <c r="P10" s="18"/>
     </row>
-    <row r="11" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
         <v>3</v>
       </c>
@@ -13885,7 +13885,7 @@
       <c r="O11" s="17"/>
       <c r="P11" s="18"/>
     </row>
-    <row r="12" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="16" t="s">
         <v>3</v>
       </c>
@@ -13906,7 +13906,7 @@
       <c r="O12" s="17"/>
       <c r="P12" s="18"/>
     </row>
-    <row r="13" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="16" t="s">
         <v>4</v>
       </c>
@@ -13927,7 +13927,7 @@
       <c r="O13" s="17"/>
       <c r="P13" s="18"/>
     </row>
-    <row r="14" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
         <v>4</v>
       </c>
@@ -13948,7 +13948,7 @@
       <c r="O14" s="17"/>
       <c r="P14" s="18"/>
     </row>
-    <row r="15" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
         <v>4</v>
       </c>
@@ -13969,7 +13969,7 @@
       <c r="O15" s="17"/>
       <c r="P15" s="18"/>
     </row>
-    <row r="16" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="16" t="s">
         <v>4</v>
       </c>
@@ -13990,7 +13990,7 @@
       <c r="O16" s="17"/>
       <c r="P16" s="18"/>
     </row>
-    <row r="17" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="16" t="s">
         <v>5</v>
       </c>
@@ -14011,7 +14011,7 @@
       <c r="O17" s="17"/>
       <c r="P17" s="18"/>
     </row>
-    <row r="18" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="16" t="s">
         <v>5</v>
       </c>
@@ -14032,7 +14032,7 @@
       <c r="O18" s="17"/>
       <c r="P18" s="18"/>
     </row>
-    <row r="19" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="16" t="s">
         <v>5</v>
       </c>
@@ -14053,7 +14053,7 @@
       <c r="O19" s="17"/>
       <c r="P19" s="18"/>
     </row>
-    <row r="20" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="16" t="s">
         <v>5</v>
       </c>
@@ -14074,7 +14074,7 @@
       <c r="O20" s="17"/>
       <c r="P20" s="18"/>
     </row>
-    <row r="21" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="16" t="s">
         <v>6</v>
       </c>
@@ -14095,7 +14095,7 @@
       <c r="O21" s="17"/>
       <c r="P21" s="18"/>
     </row>
-    <row r="22" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="16" t="s">
         <v>6</v>
       </c>
@@ -14116,7 +14116,7 @@
       <c r="O22" s="17"/>
       <c r="P22" s="18"/>
     </row>
-    <row r="23" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="16" t="s">
         <v>6</v>
       </c>
@@ -14139,7 +14139,7 @@
       <c r="O23" s="17"/>
       <c r="P23" s="18"/>
     </row>
-    <row r="24" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="16" t="s">
         <v>6</v>
       </c>
@@ -14160,7 +14160,7 @@
       <c r="O24" s="17"/>
       <c r="P24" s="18"/>
     </row>
-    <row r="25" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>36</v>
       </c>
@@ -14181,7 +14181,7 @@
       <c r="O25" s="17"/>
       <c r="P25" s="18"/>
     </row>
-    <row r="26" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="16" t="s">
         <v>36</v>
       </c>
@@ -14202,7 +14202,7 @@
       <c r="O26" s="17"/>
       <c r="P26" s="18"/>
     </row>
-    <row r="27" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="16" t="s">
         <v>36</v>
       </c>
@@ -14223,7 +14223,7 @@
       <c r="O27" s="17"/>
       <c r="P27" s="18"/>
     </row>
-    <row r="28" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="16" t="s">
         <v>36</v>
       </c>
@@ -14244,7 +14244,7 @@
       <c r="O28" s="17"/>
       <c r="P28" s="18"/>
     </row>
-    <row r="29" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="16" t="s">
         <v>37</v>
       </c>
@@ -14265,7 +14265,7 @@
       <c r="O29" s="17"/>
       <c r="P29" s="18"/>
     </row>
-    <row r="30" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="16" t="s">
         <v>37</v>
       </c>
@@ -14286,7 +14286,7 @@
       <c r="O30" s="17"/>
       <c r="P30" s="18"/>
     </row>
-    <row r="31" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="16" t="s">
         <v>37</v>
       </c>
@@ -14307,7 +14307,7 @@
       <c r="O31" s="17"/>
       <c r="P31" s="18"/>
     </row>
-    <row r="32" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="16" t="s">
         <v>37</v>
       </c>
@@ -14328,7 +14328,7 @@
       <c r="O32" s="17"/>
       <c r="P32" s="18"/>
     </row>
-    <row r="33" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="16" t="s">
         <v>38</v>
       </c>
@@ -14349,7 +14349,7 @@
       <c r="O33" s="17"/>
       <c r="P33" s="18"/>
     </row>
-    <row r="34" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="16" t="s">
         <v>38</v>
       </c>
@@ -14370,7 +14370,7 @@
       <c r="O34" s="17"/>
       <c r="P34" s="18"/>
     </row>
-    <row r="35" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="16" t="s">
         <v>38</v>
       </c>
@@ -14391,7 +14391,7 @@
       <c r="O35" s="17"/>
       <c r="P35" s="18"/>
     </row>
-    <row r="36" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="16" t="s">
         <v>38</v>
       </c>
@@ -14412,7 +14412,7 @@
       <c r="O36" s="17"/>
       <c r="P36" s="18"/>
     </row>
-    <row r="37" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="16" t="s">
         <v>39</v>
       </c>
@@ -14433,7 +14433,7 @@
       <c r="O37" s="17"/>
       <c r="P37" s="18"/>
     </row>
-    <row r="38" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="16" t="s">
         <v>39</v>
       </c>
@@ -14454,7 +14454,7 @@
       <c r="O38" s="17"/>
       <c r="P38" s="18"/>
     </row>
-    <row r="39" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="16" t="s">
         <v>39</v>
       </c>
@@ -14475,7 +14475,7 @@
       <c r="O39" s="17"/>
       <c r="P39" s="18"/>
     </row>
-    <row r="40" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="16" t="s">
         <v>39</v>
       </c>
@@ -14496,7 +14496,7 @@
       <c r="O40" s="17"/>
       <c r="P40" s="18"/>
     </row>
-    <row r="41" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="16" t="s">
         <v>40</v>
       </c>
@@ -14517,7 +14517,7 @@
       <c r="O41" s="17"/>
       <c r="P41" s="18"/>
     </row>
-    <row r="42" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="16" t="s">
         <v>40</v>
       </c>
@@ -14538,7 +14538,7 @@
       <c r="O42" s="17"/>
       <c r="P42" s="18"/>
     </row>
-    <row r="43" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="16" t="s">
         <v>40</v>
       </c>
@@ -14559,7 +14559,7 @@
       <c r="O43" s="17"/>
       <c r="P43" s="18"/>
     </row>
-    <row r="44" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="16" t="s">
         <v>40</v>
       </c>
@@ -14580,7 +14580,7 @@
       <c r="O44" s="17"/>
       <c r="P44" s="18"/>
     </row>
-    <row r="45" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="16" t="s">
         <v>41</v>
       </c>
@@ -14601,7 +14601,7 @@
       <c r="O45" s="17"/>
       <c r="P45" s="18"/>
     </row>
-    <row r="46" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="16" t="s">
         <v>41</v>
       </c>
@@ -14622,7 +14622,7 @@
       <c r="O46" s="17"/>
       <c r="P46" s="18"/>
     </row>
-    <row r="47" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="16" t="s">
         <v>41</v>
       </c>
@@ -14643,7 +14643,7 @@
       <c r="O47" s="17"/>
       <c r="P47" s="18"/>
     </row>
-    <row r="48" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="16" t="s">
         <v>41</v>
       </c>
@@ -14664,7 +14664,7 @@
       <c r="O48" s="17"/>
       <c r="P48" s="18"/>
     </row>
-    <row r="49" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="16" t="s">
         <v>42</v>
       </c>
@@ -14685,7 +14685,7 @@
       <c r="O49" s="17"/>
       <c r="P49" s="18"/>
     </row>
-    <row r="50" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="16" t="s">
         <v>42</v>
       </c>
@@ -14706,7 +14706,7 @@
       <c r="O50" s="17"/>
       <c r="P50" s="18"/>
     </row>
-    <row r="51" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="16" t="s">
         <v>42</v>
       </c>
@@ -14727,7 +14727,7 @@
       <c r="O51" s="17"/>
       <c r="P51" s="18"/>
     </row>
-    <row r="52" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="16" t="s">
         <v>42</v>
       </c>
@@ -14748,7 +14748,7 @@
       <c r="O52" s="17"/>
       <c r="P52" s="18"/>
     </row>
-    <row r="53" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="16" t="s">
         <v>43</v>
       </c>
@@ -14769,7 +14769,7 @@
       <c r="O53" s="17"/>
       <c r="P53" s="18"/>
     </row>
-    <row r="54" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="16" t="s">
         <v>43</v>
       </c>
@@ -14790,7 +14790,7 @@
       <c r="O54" s="17"/>
       <c r="P54" s="18"/>
     </row>
-    <row r="55" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="16" t="s">
         <v>43</v>
       </c>
@@ -14811,7 +14811,7 @@
       <c r="O55" s="17"/>
       <c r="P55" s="18"/>
     </row>
-    <row r="56" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="16" t="s">
         <v>43</v>
       </c>
@@ -14832,7 +14832,7 @@
       <c r="O56" s="17"/>
       <c r="P56" s="18"/>
     </row>
-    <row r="57" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="16" t="s">
         <v>44</v>
       </c>
@@ -14853,7 +14853,7 @@
       <c r="O57" s="17"/>
       <c r="P57" s="18"/>
     </row>
-    <row r="58" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="16" t="s">
         <v>44</v>
       </c>
@@ -14874,7 +14874,7 @@
       <c r="O58" s="17"/>
       <c r="P58" s="18"/>
     </row>
-    <row r="59" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="16" t="s">
         <v>44</v>
       </c>
@@ -14895,7 +14895,7 @@
       <c r="O59" s="17"/>
       <c r="P59" s="18"/>
     </row>
-    <row r="60" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="16" t="s">
         <v>44</v>
       </c>
@@ -14916,7 +14916,7 @@
       <c r="O60" s="17"/>
       <c r="P60" s="18"/>
     </row>
-    <row r="61" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="16" t="s">
         <v>45</v>
       </c>
@@ -14937,7 +14937,7 @@
       <c r="O61" s="17"/>
       <c r="P61" s="18"/>
     </row>
-    <row r="62" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="16" t="s">
         <v>45</v>
       </c>
@@ -14958,7 +14958,7 @@
       <c r="O62" s="17"/>
       <c r="P62" s="18"/>
     </row>
-    <row r="63" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="16" t="s">
         <v>45</v>
       </c>
@@ -14979,7 +14979,7 @@
       <c r="O63" s="17"/>
       <c r="P63" s="18"/>
     </row>
-    <row r="64" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="16" t="s">
         <v>45</v>
       </c>
@@ -15000,7 +15000,7 @@
       <c r="O64" s="17"/>
       <c r="P64" s="18"/>
     </row>
-    <row r="65" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="16" t="s">
         <v>46</v>
       </c>
@@ -15021,7 +15021,7 @@
       <c r="O65" s="17"/>
       <c r="P65" s="18"/>
     </row>
-    <row r="66" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="16" t="s">
         <v>46</v>
       </c>
@@ -15042,7 +15042,7 @@
       <c r="O66" s="17"/>
       <c r="P66" s="18"/>
     </row>
-    <row r="67" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="16" t="s">
         <v>46</v>
       </c>
@@ -15063,7 +15063,7 @@
       <c r="O67" s="17"/>
       <c r="P67" s="18"/>
     </row>
-    <row r="68" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="16" t="s">
         <v>46</v>
       </c>
@@ -15084,7 +15084,7 @@
       <c r="O68" s="17"/>
       <c r="P68" s="18"/>
     </row>
-    <row r="69" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="16" t="s">
         <v>47</v>
       </c>
@@ -15105,7 +15105,7 @@
       <c r="O69" s="17"/>
       <c r="P69" s="18"/>
     </row>
-    <row r="70" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="16" t="s">
         <v>47</v>
       </c>
@@ -15126,7 +15126,7 @@
       <c r="O70" s="17"/>
       <c r="P70" s="18"/>
     </row>
-    <row r="71" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="16" t="s">
         <v>47</v>
       </c>
@@ -15147,7 +15147,7 @@
       <c r="O71" s="17"/>
       <c r="P71" s="18"/>
     </row>
-    <row r="72" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="16" t="s">
         <v>47</v>
       </c>
@@ -15168,7 +15168,7 @@
       <c r="O72" s="17"/>
       <c r="P72" s="18"/>
     </row>
-    <row r="73" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="16" t="s">
         <v>48</v>
       </c>
@@ -15189,7 +15189,7 @@
       <c r="O73" s="17"/>
       <c r="P73" s="18"/>
     </row>
-    <row r="74" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="16" t="s">
         <v>48</v>
       </c>
@@ -15210,7 +15210,7 @@
       <c r="O74" s="17"/>
       <c r="P74" s="18"/>
     </row>
-    <row r="75" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="16" t="s">
         <v>48</v>
       </c>
@@ -15231,7 +15231,7 @@
       <c r="O75" s="17"/>
       <c r="P75" s="18"/>
     </row>
-    <row r="76" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="16" t="s">
         <v>49</v>
       </c>
@@ -15252,7 +15252,7 @@
       <c r="O76" s="17"/>
       <c r="P76" s="18"/>
     </row>
-    <row r="77" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="16" t="s">
         <v>49</v>
       </c>
@@ -15273,7 +15273,7 @@
       <c r="O77" s="17"/>
       <c r="P77" s="18"/>
     </row>
-    <row r="78" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="16" t="s">
         <v>49</v>
       </c>
@@ -15294,7 +15294,7 @@
       <c r="O78" s="17"/>
       <c r="P78" s="18"/>
     </row>
-    <row r="79" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="16" t="s">
         <v>49</v>
       </c>
@@ -15315,7 +15315,7 @@
       <c r="O79" s="17"/>
       <c r="P79" s="18"/>
     </row>
-    <row r="80" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="16" t="s">
         <v>50</v>
       </c>
@@ -15336,7 +15336,7 @@
       <c r="O80" s="17"/>
       <c r="P80" s="18"/>
     </row>
-    <row r="81" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="16" t="s">
         <v>50</v>
       </c>
@@ -15357,7 +15357,7 @@
       <c r="O81" s="17"/>
       <c r="P81" s="18"/>
     </row>
-    <row r="82" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="16" t="s">
         <v>50</v>
       </c>
@@ -15378,7 +15378,7 @@
       <c r="O82" s="17"/>
       <c r="P82" s="18"/>
     </row>
-    <row r="83" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="16" t="s">
         <v>50</v>
       </c>
@@ -15399,7 +15399,7 @@
       <c r="O83" s="17"/>
       <c r="P83" s="18"/>
     </row>
-    <row r="84" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="16" t="s">
         <v>51</v>
       </c>
@@ -15420,7 +15420,7 @@
       <c r="O84" s="17"/>
       <c r="P84" s="18"/>
     </row>
-    <row r="85" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="16" t="s">
         <v>51</v>
       </c>
@@ -15441,7 +15441,7 @@
       <c r="O85" s="17"/>
       <c r="P85" s="18"/>
     </row>
-    <row r="86" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="16" t="s">
         <v>51</v>
       </c>
@@ -15462,7 +15462,7 @@
       <c r="O86" s="17"/>
       <c r="P86" s="18"/>
     </row>
-    <row r="87" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="16" t="s">
         <v>51</v>
       </c>
@@ -15483,7 +15483,7 @@
       <c r="O87" s="17"/>
       <c r="P87" s="18"/>
     </row>
-    <row r="88" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="16" t="s">
         <v>52</v>
       </c>
@@ -15504,7 +15504,7 @@
       <c r="O88" s="17"/>
       <c r="P88" s="18"/>
     </row>
-    <row r="89" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="16" t="s">
         <v>52</v>
       </c>
@@ -15525,7 +15525,7 @@
       <c r="O89" s="17"/>
       <c r="P89" s="18"/>
     </row>
-    <row r="90" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="16" t="s">
         <v>52</v>
       </c>
@@ -15546,7 +15546,7 @@
       <c r="O90" s="17"/>
       <c r="P90" s="18"/>
     </row>
-    <row r="91" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="16" t="s">
         <v>52</v>
       </c>
@@ -15567,7 +15567,7 @@
       <c r="O91" s="17"/>
       <c r="P91" s="18"/>
     </row>
-    <row r="92" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="16" t="s">
         <v>53</v>
       </c>
@@ -15588,7 +15588,7 @@
       <c r="O92" s="17"/>
       <c r="P92" s="18"/>
     </row>
-    <row r="93" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="16" t="s">
         <v>53</v>
       </c>
@@ -15609,7 +15609,7 @@
       <c r="O93" s="17"/>
       <c r="P93" s="18"/>
     </row>
-    <row r="94" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="16" t="s">
         <v>53</v>
       </c>
@@ -15630,7 +15630,7 @@
       <c r="O94" s="17"/>
       <c r="P94" s="18"/>
     </row>
-    <row r="95" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="16" t="s">
         <v>53</v>
       </c>
@@ -15651,7 +15651,7 @@
       <c r="O95" s="17"/>
       <c r="P95" s="18"/>
     </row>
-    <row r="96" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="16" t="s">
         <v>54</v>
       </c>
@@ -15672,7 +15672,7 @@
       <c r="O96" s="17"/>
       <c r="P96" s="18"/>
     </row>
-    <row r="97" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="16" t="s">
         <v>54</v>
       </c>
@@ -15693,7 +15693,7 @@
       <c r="O97" s="17"/>
       <c r="P97" s="18"/>
     </row>
-    <row r="98" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="16" t="s">
         <v>54</v>
       </c>
@@ -15714,7 +15714,7 @@
       <c r="O98" s="17"/>
       <c r="P98" s="18"/>
     </row>
-    <row r="99" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="16" t="s">
         <v>54</v>
       </c>
@@ -15735,7 +15735,7 @@
       <c r="O99" s="17"/>
       <c r="P99" s="18"/>
     </row>
-    <row r="100" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="16" t="s">
         <v>55</v>
       </c>
@@ -15756,7 +15756,7 @@
       <c r="O100" s="17"/>
       <c r="P100" s="18"/>
     </row>
-    <row r="101" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="16" t="s">
         <v>55</v>
       </c>
@@ -15777,7 +15777,7 @@
       <c r="O101" s="17"/>
       <c r="P101" s="18"/>
     </row>
-    <row r="102" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="16" t="s">
         <v>55</v>
       </c>
@@ -15798,7 +15798,7 @@
       <c r="O102" s="17"/>
       <c r="P102" s="18"/>
     </row>
-    <row r="103" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="16" t="s">
         <v>55</v>
       </c>
@@ -15819,7 +15819,7 @@
       <c r="O103" s="17"/>
       <c r="P103" s="18"/>
     </row>
-    <row r="104" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="16" t="s">
         <v>56</v>
       </c>
@@ -15840,7 +15840,7 @@
       <c r="O104" s="17"/>
       <c r="P104" s="18"/>
     </row>
-    <row r="105" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="16" t="s">
         <v>56</v>
       </c>
@@ -15861,7 +15861,7 @@
       <c r="O105" s="17"/>
       <c r="P105" s="18"/>
     </row>
-    <row r="106" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="16" t="s">
         <v>56</v>
       </c>
@@ -15882,7 +15882,7 @@
       <c r="O106" s="17"/>
       <c r="P106" s="18"/>
     </row>
-    <row r="107" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="16" t="s">
         <v>56</v>
       </c>
@@ -15903,7 +15903,7 @@
       <c r="O107" s="17"/>
       <c r="P107" s="18"/>
     </row>
-    <row r="108" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="16" t="s">
         <v>57</v>
       </c>
@@ -15924,7 +15924,7 @@
       <c r="O108" s="17"/>
       <c r="P108" s="18"/>
     </row>
-    <row r="109" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="16" t="s">
         <v>57</v>
       </c>
@@ -15945,7 +15945,7 @@
       <c r="O109" s="17"/>
       <c r="P109" s="18"/>
     </row>
-    <row r="110" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="16" t="s">
         <v>57</v>
       </c>
@@ -15966,7 +15966,7 @@
       <c r="O110" s="17"/>
       <c r="P110" s="18"/>
     </row>
-    <row r="111" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="16" t="s">
         <v>58</v>
       </c>
@@ -15987,7 +15987,7 @@
       <c r="O111" s="17"/>
       <c r="P111" s="18"/>
     </row>
-    <row r="112" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="16" t="s">
         <v>58</v>
       </c>
@@ -16008,7 +16008,7 @@
       <c r="O112" s="17"/>
       <c r="P112" s="18"/>
     </row>
-    <row r="113" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="16" t="s">
         <v>58</v>
       </c>
@@ -16029,7 +16029,7 @@
       <c r="O113" s="17"/>
       <c r="P113" s="18"/>
     </row>
-    <row r="114" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="16" t="s">
         <v>58</v>
       </c>
@@ -16050,7 +16050,7 @@
       <c r="O114" s="17"/>
       <c r="P114" s="18"/>
     </row>
-    <row r="115" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="16" t="s">
         <v>59</v>
       </c>
@@ -16071,7 +16071,7 @@
       <c r="O115" s="17"/>
       <c r="P115" s="18"/>
     </row>
-    <row r="116" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="16" t="s">
         <v>59</v>
       </c>
@@ -16092,7 +16092,7 @@
       <c r="O116" s="17"/>
       <c r="P116" s="18"/>
     </row>
-    <row r="117" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="16" t="s">
         <v>59</v>
       </c>
@@ -16113,7 +16113,7 @@
       <c r="O117" s="17"/>
       <c r="P117" s="18"/>
     </row>
-    <row r="118" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="16" t="s">
         <v>59</v>
       </c>
@@ -16134,7 +16134,7 @@
       <c r="O118" s="17"/>
       <c r="P118" s="18"/>
     </row>
-    <row r="119" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="16" t="s">
         <v>60</v>
       </c>
@@ -16155,7 +16155,7 @@
       <c r="O119" s="17"/>
       <c r="P119" s="18"/>
     </row>
-    <row r="120" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="16" t="s">
         <v>60</v>
       </c>
@@ -16176,7 +16176,7 @@
       <c r="O120" s="17"/>
       <c r="P120" s="18"/>
     </row>
-    <row r="121" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B121" s="16" t="s">
         <v>60</v>
       </c>
@@ -16197,7 +16197,7 @@
       <c r="O121" s="17"/>
       <c r="P121" s="18"/>
     </row>
-    <row r="122" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="16" t="s">
         <v>60</v>
       </c>
@@ -16218,7 +16218,7 @@
       <c r="O122" s="17"/>
       <c r="P122" s="18"/>
     </row>
-    <row r="123" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="16" t="s">
         <v>61</v>
       </c>
@@ -16239,7 +16239,7 @@
       <c r="O123" s="17"/>
       <c r="P123" s="18"/>
     </row>
-    <row r="124" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="16" t="s">
         <v>61</v>
       </c>
@@ -16260,7 +16260,7 @@
       <c r="O124" s="17"/>
       <c r="P124" s="18"/>
     </row>
-    <row r="125" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B125" s="16" t="s">
         <v>61</v>
       </c>
@@ -16281,7 +16281,7 @@
       <c r="O125" s="17"/>
       <c r="P125" s="18"/>
     </row>
-    <row r="126" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="16" t="s">
         <v>61</v>
       </c>
@@ -16302,7 +16302,7 @@
       <c r="O126" s="17"/>
       <c r="P126" s="18"/>
     </row>
-    <row r="127" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B127" s="16" t="s">
         <v>62</v>
       </c>
@@ -16323,7 +16323,7 @@
       <c r="O127" s="17"/>
       <c r="P127" s="18"/>
     </row>
-    <row r="128" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B128" s="16" t="s">
         <v>62</v>
       </c>
@@ -16344,7 +16344,7 @@
       <c r="O128" s="17"/>
       <c r="P128" s="18"/>
     </row>
-    <row r="129" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B129" s="16" t="s">
         <v>62</v>
       </c>
@@ -16365,7 +16365,7 @@
       <c r="O129" s="17"/>
       <c r="P129" s="18"/>
     </row>
-    <row r="130" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B130" s="16" t="s">
         <v>62</v>
       </c>
@@ -16386,7 +16386,7 @@
       <c r="O130" s="17"/>
       <c r="P130" s="18"/>
     </row>
-    <row r="131" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B131" s="16" t="s">
         <v>63</v>
       </c>
@@ -16407,7 +16407,7 @@
       <c r="O131" s="17"/>
       <c r="P131" s="18"/>
     </row>
-    <row r="132" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B132" s="16" t="s">
         <v>63</v>
       </c>
@@ -16428,7 +16428,7 @@
       <c r="O132" s="17"/>
       <c r="P132" s="18"/>
     </row>
-    <row r="133" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B133" s="16" t="s">
         <v>63</v>
       </c>
@@ -16449,7 +16449,7 @@
       <c r="O133" s="17"/>
       <c r="P133" s="18"/>
     </row>
-    <row r="134" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B134" s="16" t="s">
         <v>63</v>
       </c>
@@ -16470,7 +16470,7 @@
       <c r="O134" s="17"/>
       <c r="P134" s="18"/>
     </row>
-    <row r="135" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B135" s="16" t="s">
         <v>64</v>
       </c>
@@ -16491,7 +16491,7 @@
       <c r="O135" s="17"/>
       <c r="P135" s="18"/>
     </row>
-    <row r="136" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B136" s="16" t="s">
         <v>64</v>
       </c>
@@ -16512,7 +16512,7 @@
       <c r="O136" s="17"/>
       <c r="P136" s="18"/>
     </row>
-    <row r="137" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B137" s="16" t="s">
         <v>64</v>
       </c>
@@ -16533,7 +16533,7 @@
       <c r="O137" s="17"/>
       <c r="P137" s="18"/>
     </row>
-    <row r="138" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B138" s="16" t="s">
         <v>64</v>
       </c>
@@ -16554,7 +16554,7 @@
       <c r="O138" s="17"/>
       <c r="P138" s="18"/>
     </row>
-    <row r="139" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B139" s="16" t="s">
         <v>65</v>
       </c>
@@ -16575,7 +16575,7 @@
       <c r="O139" s="17"/>
       <c r="P139" s="18"/>
     </row>
-    <row r="140" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="16" t="s">
         <v>65</v>
       </c>
@@ -16596,7 +16596,7 @@
       <c r="O140" s="17"/>
       <c r="P140" s="18"/>
     </row>
-    <row r="141" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="16" t="s">
         <v>65</v>
       </c>
@@ -16617,7 +16617,7 @@
       <c r="O141" s="17"/>
       <c r="P141" s="18"/>
     </row>
-    <row r="142" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B142" s="16" t="s">
         <v>65</v>
       </c>
@@ -16638,7 +16638,7 @@
       <c r="O142" s="17"/>
       <c r="P142" s="18"/>
     </row>
-    <row r="143" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B143" s="16" t="s">
         <v>66</v>
       </c>
@@ -16659,7 +16659,7 @@
       <c r="O143" s="17"/>
       <c r="P143" s="18"/>
     </row>
-    <row r="144" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B144" s="16" t="s">
         <v>66</v>
       </c>
@@ -16680,7 +16680,7 @@
       <c r="O144" s="17"/>
       <c r="P144" s="18"/>
     </row>
-    <row r="145" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B145" s="16" t="s">
         <v>66</v>
       </c>
@@ -16701,7 +16701,7 @@
       <c r="O145" s="17"/>
       <c r="P145" s="18"/>
     </row>
-    <row r="146" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B146" s="16" t="s">
         <v>66</v>
       </c>
@@ -16722,7 +16722,7 @@
       <c r="O146" s="17"/>
       <c r="P146" s="18"/>
     </row>
-    <row r="147" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B147" s="16" t="s">
         <v>67</v>
       </c>
@@ -16743,7 +16743,7 @@
       <c r="O147" s="17"/>
       <c r="P147" s="18"/>
     </row>
-    <row r="148" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B148" s="16" t="s">
         <v>67</v>
       </c>
@@ -16764,7 +16764,7 @@
       <c r="O148" s="17"/>
       <c r="P148" s="18"/>
     </row>
-    <row r="149" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B149" s="16" t="s">
         <v>67</v>
       </c>
@@ -16785,7 +16785,7 @@
       <c r="O149" s="17"/>
       <c r="P149" s="18"/>
     </row>
-    <row r="150" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B150" s="16" t="s">
         <v>67</v>
       </c>
@@ -16806,7 +16806,7 @@
       <c r="O150" s="17"/>
       <c r="P150" s="18"/>
     </row>
-    <row r="151" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B151" s="16" t="s">
         <v>68</v>
       </c>
@@ -16827,7 +16827,7 @@
       <c r="O151" s="17"/>
       <c r="P151" s="18"/>
     </row>
-    <row r="152" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B152" s="16" t="s">
         <v>68</v>
       </c>
@@ -16848,7 +16848,7 @@
       <c r="O152" s="17"/>
       <c r="P152" s="18"/>
     </row>
-    <row r="153" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B153" s="16" t="s">
         <v>68</v>
       </c>
@@ -16869,7 +16869,7 @@
       <c r="O153" s="17"/>
       <c r="P153" s="18"/>
     </row>
-    <row r="154" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="16" t="s">
         <v>68</v>
       </c>
@@ -16890,7 +16890,7 @@
       <c r="O154" s="17"/>
       <c r="P154" s="18"/>
     </row>
-    <row r="155" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B155" s="16" t="s">
         <v>69</v>
       </c>
@@ -16911,7 +16911,7 @@
       <c r="O155" s="17"/>
       <c r="P155" s="18"/>
     </row>
-    <row r="156" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B156" s="16" t="s">
         <v>69</v>
       </c>
@@ -16932,7 +16932,7 @@
       <c r="O156" s="17"/>
       <c r="P156" s="18"/>
     </row>
-    <row r="157" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B157" s="16" t="s">
         <v>69</v>
       </c>
@@ -16953,7 +16953,7 @@
       <c r="O157" s="17"/>
       <c r="P157" s="18"/>
     </row>
-    <row r="158" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B158" s="16" t="s">
         <v>69</v>
       </c>
@@ -16974,7 +16974,7 @@
       <c r="O158" s="17"/>
       <c r="P158" s="18"/>
     </row>
-    <row r="159" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B159" s="16" t="s">
         <v>70</v>
       </c>
@@ -16995,7 +16995,7 @@
       <c r="O159" s="17"/>
       <c r="P159" s="18"/>
     </row>
-    <row r="160" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B160" s="16" t="s">
         <v>70</v>
       </c>
@@ -17016,7 +17016,7 @@
       <c r="O160" s="17"/>
       <c r="P160" s="18"/>
     </row>
-    <row r="161" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B161" s="16" t="s">
         <v>70</v>
       </c>
@@ -17037,7 +17037,7 @@
       <c r="O161" s="17"/>
       <c r="P161" s="18"/>
     </row>
-    <row r="162" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B162" s="16" t="s">
         <v>70</v>
       </c>
@@ -17058,7 +17058,7 @@
       <c r="O162" s="17"/>
       <c r="P162" s="18"/>
     </row>
-    <row r="163" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B163" s="16" t="s">
         <v>71</v>
       </c>
@@ -17079,7 +17079,7 @@
       <c r="O163" s="17"/>
       <c r="P163" s="18"/>
     </row>
-    <row r="164" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B164" s="16" t="s">
         <v>71</v>
       </c>
@@ -17100,7 +17100,7 @@
       <c r="O164" s="17"/>
       <c r="P164" s="18"/>
     </row>
-    <row r="165" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B165" s="16" t="s">
         <v>71</v>
       </c>
@@ -17121,7 +17121,7 @@
       <c r="O165" s="17"/>
       <c r="P165" s="18"/>
     </row>
-    <row r="166" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B166" s="16" t="s">
         <v>71</v>
       </c>
@@ -17142,7 +17142,7 @@
       <c r="O166" s="17"/>
       <c r="P166" s="18"/>
     </row>
-    <row r="167" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="16" t="s">
         <v>72</v>
       </c>
@@ -17163,7 +17163,7 @@
       <c r="O167" s="17"/>
       <c r="P167" s="18"/>
     </row>
-    <row r="168" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="16" t="s">
         <v>72</v>
       </c>
@@ -17184,7 +17184,7 @@
       <c r="O168" s="17"/>
       <c r="P168" s="18"/>
     </row>
-    <row r="169" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B169" s="16" t="s">
         <v>72</v>
       </c>
@@ -17205,7 +17205,7 @@
       <c r="O169" s="17"/>
       <c r="P169" s="18"/>
     </row>
-    <row r="170" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B170" s="16" t="s">
         <v>72</v>
       </c>
@@ -17226,7 +17226,7 @@
       <c r="O170" s="17"/>
       <c r="P170" s="18"/>
     </row>
-    <row r="171" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B171" s="16" t="s">
         <v>73</v>
       </c>
@@ -17247,7 +17247,7 @@
       <c r="O171" s="17"/>
       <c r="P171" s="18"/>
     </row>
-    <row r="172" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B172" s="16" t="s">
         <v>73</v>
       </c>
@@ -17268,7 +17268,7 @@
       <c r="O172" s="17"/>
       <c r="P172" s="18"/>
     </row>
-    <row r="173" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B173" s="16" t="s">
         <v>73</v>
       </c>
@@ -17289,7 +17289,7 @@
       <c r="O173" s="17"/>
       <c r="P173" s="18"/>
     </row>
-    <row r="174" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B174" s="16" t="s">
         <v>73</v>
       </c>
@@ -17310,7 +17310,7 @@
       <c r="O174" s="17"/>
       <c r="P174" s="18"/>
     </row>
-    <row r="175" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B175" s="16" t="s">
         <v>74</v>
       </c>
@@ -17331,7 +17331,7 @@
       <c r="O175" s="17"/>
       <c r="P175" s="18"/>
     </row>
-    <row r="176" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B176" s="16" t="s">
         <v>74</v>
       </c>
@@ -17352,7 +17352,7 @@
       <c r="O176" s="17"/>
       <c r="P176" s="18"/>
     </row>
-    <row r="177" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B177" s="16" t="s">
         <v>74</v>
       </c>
@@ -17373,7 +17373,7 @@
       <c r="O177" s="17"/>
       <c r="P177" s="18"/>
     </row>
-    <row r="178" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B178" s="16" t="s">
         <v>74</v>
       </c>
@@ -17394,7 +17394,7 @@
       <c r="O178" s="17"/>
       <c r="P178" s="18"/>
     </row>
-    <row r="179" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B179" s="16" t="s">
         <v>75</v>
       </c>
@@ -17415,7 +17415,7 @@
       <c r="O179" s="17"/>
       <c r="P179" s="18"/>
     </row>
-    <row r="180" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B180" s="16" t="s">
         <v>75</v>
       </c>
@@ -17436,7 +17436,7 @@
       <c r="O180" s="17"/>
       <c r="P180" s="18"/>
     </row>
-    <row r="181" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B181" s="16" t="s">
         <v>75</v>
       </c>
@@ -17457,7 +17457,7 @@
       <c r="O181" s="17"/>
       <c r="P181" s="18"/>
     </row>
-    <row r="182" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B182" s="16" t="s">
         <v>75</v>
       </c>
@@ -17478,7 +17478,7 @@
       <c r="O182" s="17"/>
       <c r="P182" s="18"/>
     </row>
-    <row r="183" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B183" s="16" t="s">
         <v>76</v>
       </c>
@@ -17499,7 +17499,7 @@
       <c r="O183" s="17"/>
       <c r="P183" s="18"/>
     </row>
-    <row r="184" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B184" s="16" t="s">
         <v>76</v>
       </c>
@@ -17520,7 +17520,7 @@
       <c r="O184" s="17"/>
       <c r="P184" s="18"/>
     </row>
-    <row r="185" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B185" s="16" t="s">
         <v>76</v>
       </c>
@@ -17541,7 +17541,7 @@
       <c r="O185" s="17"/>
       <c r="P185" s="18"/>
     </row>
-    <row r="186" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="186" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B186" s="16" t="s">
         <v>76</v>
       </c>
@@ -17562,7 +17562,7 @@
       <c r="O186" s="17"/>
       <c r="P186" s="18"/>
     </row>
-    <row r="187" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B187" s="16" t="s">
         <v>77</v>
       </c>
@@ -17583,7 +17583,7 @@
       <c r="O187" s="17"/>
       <c r="P187" s="18"/>
     </row>
-    <row r="188" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B188" s="16" t="s">
         <v>77</v>
       </c>
@@ -17604,7 +17604,7 @@
       <c r="O188" s="17"/>
       <c r="P188" s="18"/>
     </row>
-    <row r="189" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B189" s="16" t="s">
         <v>77</v>
       </c>
@@ -17625,7 +17625,7 @@
       <c r="O189" s="17"/>
       <c r="P189" s="18"/>
     </row>
-    <row r="190" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B190" s="16" t="s">
         <v>77</v>
       </c>
@@ -17646,7 +17646,7 @@
       <c r="O190" s="17"/>
       <c r="P190" s="18"/>
     </row>
-    <row r="191" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B191" s="16" t="s">
         <v>78</v>
       </c>
@@ -17667,7 +17667,7 @@
       <c r="O191" s="17"/>
       <c r="P191" s="18"/>
     </row>
-    <row r="192" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B192" s="16" t="s">
         <v>78</v>
       </c>
@@ -17688,7 +17688,7 @@
       <c r="O192" s="17"/>
       <c r="P192" s="18"/>
     </row>
-    <row r="193" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B193" s="16" t="s">
         <v>78</v>
       </c>
@@ -17709,7 +17709,7 @@
       <c r="O193" s="17"/>
       <c r="P193" s="18"/>
     </row>
-    <row r="194" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B194" s="16" t="s">
         <v>78</v>
       </c>
@@ -17730,7 +17730,7 @@
       <c r="O194" s="17"/>
       <c r="P194" s="18"/>
     </row>
-    <row r="195" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B195" s="16" t="s">
         <v>79</v>
       </c>
@@ -17751,7 +17751,7 @@
       <c r="O195" s="17"/>
       <c r="P195" s="18"/>
     </row>
-    <row r="196" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B196" s="16" t="s">
         <v>79</v>
       </c>
@@ -17772,7 +17772,7 @@
       <c r="O196" s="17"/>
       <c r="P196" s="18"/>
     </row>
-    <row r="197" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B197" s="16" t="s">
         <v>79</v>
       </c>
@@ -17793,7 +17793,7 @@
       <c r="O197" s="17"/>
       <c r="P197" s="18"/>
     </row>
-    <row r="198" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B198" s="16" t="s">
         <v>79</v>
       </c>
@@ -17814,7 +17814,7 @@
       <c r="O198" s="17"/>
       <c r="P198" s="18"/>
     </row>
-    <row r="199" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B199" s="16" t="s">
         <v>80</v>
       </c>
@@ -17835,7 +17835,7 @@
       <c r="O199" s="17"/>
       <c r="P199" s="18"/>
     </row>
-    <row r="200" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B200" s="16" t="s">
         <v>80</v>
       </c>
@@ -17856,7 +17856,7 @@
       <c r="O200" s="17"/>
       <c r="P200" s="18"/>
     </row>
-    <row r="201" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B201" s="16" t="s">
         <v>80</v>
       </c>
@@ -17877,7 +17877,7 @@
       <c r="O201" s="17"/>
       <c r="P201" s="18"/>
     </row>
-    <row r="202" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B202" s="16" t="s">
         <v>80</v>
       </c>
@@ -17898,7 +17898,7 @@
       <c r="O202" s="17"/>
       <c r="P202" s="18"/>
     </row>
-    <row r="203" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B203" s="16" t="s">
         <v>81</v>
       </c>
@@ -17919,7 +17919,7 @@
       <c r="O203" s="17"/>
       <c r="P203" s="18"/>
     </row>
-    <row r="204" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B204" s="16" t="s">
         <v>81</v>
       </c>
@@ -17940,7 +17940,7 @@
       <c r="O204" s="17"/>
       <c r="P204" s="18"/>
     </row>
-    <row r="205" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B205" s="16" t="s">
         <v>81</v>
       </c>
@@ -17961,7 +17961,7 @@
       <c r="O205" s="17"/>
       <c r="P205" s="18"/>
     </row>
-    <row r="206" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B206" s="16" t="s">
         <v>81</v>
       </c>
@@ -17982,7 +17982,7 @@
       <c r="O206" s="17"/>
       <c r="P206" s="18"/>
     </row>
-    <row r="207" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B207" s="16" t="s">
         <v>82</v>
       </c>
@@ -18003,7 +18003,7 @@
       <c r="O207" s="17"/>
       <c r="P207" s="18"/>
     </row>
-    <row r="208" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B208" s="16" t="s">
         <v>82</v>
       </c>
@@ -18024,7 +18024,7 @@
       <c r="O208" s="17"/>
       <c r="P208" s="18"/>
     </row>
-    <row r="209" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B209" s="16" t="s">
         <v>82</v>
       </c>
@@ -18045,7 +18045,7 @@
       <c r="O209" s="17"/>
       <c r="P209" s="18"/>
     </row>
-    <row r="210" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B210" s="16" t="s">
         <v>82</v>
       </c>
@@ -18066,7 +18066,7 @@
       <c r="O210" s="17"/>
       <c r="P210" s="18"/>
     </row>
-    <row r="211" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B211" s="16" t="s">
         <v>83</v>
       </c>
@@ -18087,7 +18087,7 @@
       <c r="O211" s="17"/>
       <c r="P211" s="18"/>
     </row>
-    <row r="212" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B212" s="16" t="s">
         <v>83</v>
       </c>
@@ -18108,7 +18108,7 @@
       <c r="O212" s="17"/>
       <c r="P212" s="18"/>
     </row>
-    <row r="213" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B213" s="16" t="s">
         <v>83</v>
       </c>
@@ -18129,7 +18129,7 @@
       <c r="O213" s="17"/>
       <c r="P213" s="18"/>
     </row>
-    <row r="214" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B214" s="16" t="s">
         <v>83</v>
       </c>
@@ -18150,7 +18150,7 @@
       <c r="O214" s="17"/>
       <c r="P214" s="18"/>
     </row>
-    <row r="215" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B215" s="16" t="s">
         <v>84</v>
       </c>
@@ -18171,7 +18171,7 @@
       <c r="O215" s="17"/>
       <c r="P215" s="18"/>
     </row>
-    <row r="216" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B216" s="16" t="s">
         <v>84</v>
       </c>
@@ -18192,7 +18192,7 @@
       <c r="O216" s="17"/>
       <c r="P216" s="18"/>
     </row>
-    <row r="217" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B217" s="16" t="s">
         <v>84</v>
       </c>
@@ -18213,7 +18213,7 @@
       <c r="O217" s="17"/>
       <c r="P217" s="18"/>
     </row>
-    <row r="218" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B218" s="16" t="s">
         <v>84</v>
       </c>
@@ -18234,7 +18234,7 @@
       <c r="O218" s="17"/>
       <c r="P218" s="18"/>
     </row>
-    <row r="219" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B219" s="16" t="s">
         <v>85</v>
       </c>
@@ -18255,7 +18255,7 @@
       <c r="O219" s="17"/>
       <c r="P219" s="18"/>
     </row>
-    <row r="220" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B220" s="16" t="s">
         <v>85</v>
       </c>
@@ -18276,7 +18276,7 @@
       <c r="O220" s="17"/>
       <c r="P220" s="18"/>
     </row>
-    <row r="221" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B221" s="16" t="s">
         <v>85</v>
       </c>
@@ -18297,7 +18297,7 @@
       <c r="O221" s="17"/>
       <c r="P221" s="18"/>
     </row>
-    <row r="222" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B222" s="16" t="s">
         <v>85</v>
       </c>
@@ -18318,7 +18318,7 @@
       <c r="O222" s="17"/>
       <c r="P222" s="18"/>
     </row>
-    <row r="223" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B223" s="16" t="s">
         <v>86</v>
       </c>
@@ -18339,7 +18339,7 @@
       <c r="O223" s="17"/>
       <c r="P223" s="18"/>
     </row>
-    <row r="224" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B224" s="16" t="s">
         <v>86</v>
       </c>
@@ -18360,7 +18360,7 @@
       <c r="O224" s="17"/>
       <c r="P224" s="18"/>
     </row>
-    <row r="225" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B225" s="16" t="s">
         <v>86</v>
       </c>
@@ -18381,7 +18381,7 @@
       <c r="O225" s="17"/>
       <c r="P225" s="18"/>
     </row>
-    <row r="226" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B226" s="16" t="s">
         <v>86</v>
       </c>
@@ -18402,7 +18402,7 @@
       <c r="O226" s="17"/>
       <c r="P226" s="18"/>
     </row>
-    <row r="227" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B227" s="16" t="s">
         <v>87</v>
       </c>
@@ -18423,7 +18423,7 @@
       <c r="O227" s="17"/>
       <c r="P227" s="18"/>
     </row>
-    <row r="228" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B228" s="16" t="s">
         <v>87</v>
       </c>
@@ -18444,7 +18444,7 @@
       <c r="O228" s="17"/>
       <c r="P228" s="18"/>
     </row>
-    <row r="229" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B229" s="16" t="s">
         <v>87</v>
       </c>
@@ -18465,7 +18465,7 @@
       <c r="O229" s="17"/>
       <c r="P229" s="18"/>
     </row>
-    <row r="230" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B230" s="16" t="s">
         <v>87</v>
       </c>
@@ -18486,7 +18486,7 @@
       <c r="O230" s="17"/>
       <c r="P230" s="18"/>
     </row>
-    <row r="231" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B231" s="16" t="s">
         <v>88</v>
       </c>
@@ -18507,7 +18507,7 @@
       <c r="O231" s="17"/>
       <c r="P231" s="18"/>
     </row>
-    <row r="232" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B232" s="16" t="s">
         <v>88</v>
       </c>
@@ -18528,7 +18528,7 @@
       <c r="O232" s="17"/>
       <c r="P232" s="18"/>
     </row>
-    <row r="233" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B233" s="16" t="s">
         <v>88</v>
       </c>
@@ -18549,7 +18549,7 @@
       <c r="O233" s="17"/>
       <c r="P233" s="18"/>
     </row>
-    <row r="234" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B234" s="16" t="s">
         <v>88</v>
       </c>
@@ -18570,7 +18570,7 @@
       <c r="O234" s="17"/>
       <c r="P234" s="18"/>
     </row>
-    <row r="235" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B235" s="16" t="s">
         <v>89</v>
       </c>
@@ -18591,7 +18591,7 @@
       <c r="O235" s="17"/>
       <c r="P235" s="18"/>
     </row>
-    <row r="236" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B236" s="16" t="s">
         <v>89</v>
       </c>
@@ -18612,7 +18612,7 @@
       <c r="O236" s="17"/>
       <c r="P236" s="18"/>
     </row>
-    <row r="237" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B237" s="16" t="s">
         <v>89</v>
       </c>
@@ -18633,7 +18633,7 @@
       <c r="O237" s="17"/>
       <c r="P237" s="18"/>
     </row>
-    <row r="238" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B238" s="16" t="s">
         <v>89</v>
       </c>
@@ -18654,7 +18654,7 @@
       <c r="O238" s="17"/>
       <c r="P238" s="18"/>
     </row>
-    <row r="239" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B239" s="16" t="s">
         <v>90</v>
       </c>
@@ -18675,7 +18675,7 @@
       <c r="O239" s="17"/>
       <c r="P239" s="18"/>
     </row>
-    <row r="240" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B240" s="16" t="s">
         <v>90</v>
       </c>
@@ -18696,7 +18696,7 @@
       <c r="O240" s="17"/>
       <c r="P240" s="18"/>
     </row>
-    <row r="241" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B241" s="16" t="s">
         <v>90</v>
       </c>
@@ -18717,7 +18717,7 @@
       <c r="O241" s="17"/>
       <c r="P241" s="18"/>
     </row>
-    <row r="242" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B242" s="16" t="s">
         <v>90</v>
       </c>
@@ -18738,7 +18738,7 @@
       <c r="O242" s="17"/>
       <c r="P242" s="18"/>
     </row>
-    <row r="243" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B243" s="16" t="s">
         <v>91</v>
       </c>
@@ -18759,7 +18759,7 @@
       <c r="O243" s="17"/>
       <c r="P243" s="18"/>
     </row>
-    <row r="244" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B244" s="16" t="s">
         <v>91</v>
       </c>
@@ -18780,7 +18780,7 @@
       <c r="O244" s="17"/>
       <c r="P244" s="18"/>
     </row>
-    <row r="245" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B245" s="16" t="s">
         <v>91</v>
       </c>
@@ -18801,7 +18801,7 @@
       <c r="O245" s="17"/>
       <c r="P245" s="18"/>
     </row>
-    <row r="246" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B246" s="16" t="s">
         <v>91</v>
       </c>
@@ -18822,7 +18822,7 @@
       <c r="O246" s="17"/>
       <c r="P246" s="18"/>
     </row>
-    <row r="247" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B247" s="16" t="s">
         <v>92</v>
       </c>
@@ -18843,7 +18843,7 @@
       <c r="O247" s="17"/>
       <c r="P247" s="18"/>
     </row>
-    <row r="248" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B248" s="16" t="s">
         <v>92</v>
       </c>
@@ -18864,7 +18864,7 @@
       <c r="O248" s="17"/>
       <c r="P248" s="18"/>
     </row>
-    <row r="249" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B249" s="16" t="s">
         <v>92</v>
       </c>
@@ -18885,7 +18885,7 @@
       <c r="O249" s="17"/>
       <c r="P249" s="18"/>
     </row>
-    <row r="250" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B250" s="16" t="s">
         <v>92</v>
       </c>
@@ -18906,7 +18906,7 @@
       <c r="O250" s="17"/>
       <c r="P250" s="18"/>
     </row>
-    <row r="251" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B251" s="16" t="s">
         <v>93</v>
       </c>
@@ -18927,7 +18927,7 @@
       <c r="O251" s="17"/>
       <c r="P251" s="18"/>
     </row>
-    <row r="252" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B252" s="16" t="s">
         <v>93</v>
       </c>
@@ -18948,7 +18948,7 @@
       <c r="O252" s="17"/>
       <c r="P252" s="18"/>
     </row>
-    <row r="253" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B253" s="16" t="s">
         <v>93</v>
       </c>
@@ -18969,7 +18969,7 @@
       <c r="O253" s="17"/>
       <c r="P253" s="18"/>
     </row>
-    <row r="254" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B254" s="16" t="s">
         <v>93</v>
       </c>
@@ -18990,7 +18990,7 @@
       <c r="O254" s="17"/>
       <c r="P254" s="18"/>
     </row>
-    <row r="255" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B255" s="16" t="s">
         <v>94</v>
       </c>
@@ -19011,7 +19011,7 @@
       <c r="O255" s="17"/>
       <c r="P255" s="18"/>
     </row>
-    <row r="256" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B256" s="16" t="s">
         <v>94</v>
       </c>
@@ -19032,7 +19032,7 @@
       <c r="O256" s="17"/>
       <c r="P256" s="18"/>
     </row>
-    <row r="257" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B257" s="16" t="s">
         <v>94</v>
       </c>
@@ -19053,7 +19053,7 @@
       <c r="O257" s="17"/>
       <c r="P257" s="18"/>
     </row>
-    <row r="258" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B258" s="16" t="s">
         <v>94</v>
       </c>
@@ -19074,7 +19074,7 @@
       <c r="O258" s="17"/>
       <c r="P258" s="18"/>
     </row>
-    <row r="259" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B259" s="16" t="s">
         <v>95</v>
       </c>
@@ -19095,7 +19095,7 @@
       <c r="O259" s="17"/>
       <c r="P259" s="18"/>
     </row>
-    <row r="260" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B260" s="16" t="s">
         <v>95</v>
       </c>
@@ -19116,7 +19116,7 @@
       <c r="O260" s="17"/>
       <c r="P260" s="18"/>
     </row>
-    <row r="261" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B261" s="16" t="s">
         <v>95</v>
       </c>
@@ -19137,7 +19137,7 @@
       <c r="O261" s="17"/>
       <c r="P261" s="18"/>
     </row>
-    <row r="262" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B262" s="16" t="s">
         <v>95</v>
       </c>
@@ -19158,7 +19158,7 @@
       <c r="O262" s="17"/>
       <c r="P262" s="18"/>
     </row>
-    <row r="263" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B263" s="16" t="s">
         <v>96</v>
       </c>
@@ -19179,7 +19179,7 @@
       <c r="O263" s="17"/>
       <c r="P263" s="18"/>
     </row>
-    <row r="264" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B264" s="16" t="s">
         <v>96</v>
       </c>
@@ -19200,7 +19200,7 @@
       <c r="O264" s="17"/>
       <c r="P264" s="18"/>
     </row>
-    <row r="265" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B265" s="16" t="s">
         <v>96</v>
       </c>
@@ -19221,7 +19221,7 @@
       <c r="O265" s="17"/>
       <c r="P265" s="18"/>
     </row>
-    <row r="266" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B266" s="16" t="s">
         <v>97</v>
       </c>
@@ -19242,7 +19242,7 @@
       <c r="O266" s="17"/>
       <c r="P266" s="18"/>
     </row>
-    <row r="267" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B267" s="16" t="s">
         <v>97</v>
       </c>
@@ -19263,7 +19263,7 @@
       <c r="O267" s="17"/>
       <c r="P267" s="18"/>
     </row>
-    <row r="268" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B268" s="16" t="s">
         <v>97</v>
       </c>
@@ -19284,7 +19284,7 @@
       <c r="O268" s="17"/>
       <c r="P268" s="18"/>
     </row>
-    <row r="269" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B269" s="16" t="s">
         <v>97</v>
       </c>
@@ -19305,7 +19305,7 @@
       <c r="O269" s="17"/>
       <c r="P269" s="18"/>
     </row>
-    <row r="270" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B270" s="16" t="s">
         <v>98</v>
       </c>
@@ -19326,7 +19326,7 @@
       <c r="O270" s="17"/>
       <c r="P270" s="18"/>
     </row>
-    <row r="271" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B271" s="16" t="s">
         <v>98</v>
       </c>
@@ -19347,7 +19347,7 @@
       <c r="O271" s="17"/>
       <c r="P271" s="18"/>
     </row>
-    <row r="272" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B272" s="16" t="s">
         <v>98</v>
       </c>
@@ -19368,7 +19368,7 @@
       <c r="O272" s="17"/>
       <c r="P272" s="18"/>
     </row>
-    <row r="273" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B273" s="16" t="s">
         <v>98</v>
       </c>
@@ -19389,7 +19389,7 @@
       <c r="O273" s="17"/>
       <c r="P273" s="18"/>
     </row>
-    <row r="274" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B274" s="16" t="s">
         <v>99</v>
       </c>
@@ -19410,7 +19410,7 @@
       <c r="O274" s="17"/>
       <c r="P274" s="18"/>
     </row>
-    <row r="275" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B275" s="16" t="s">
         <v>99</v>
       </c>
@@ -19431,7 +19431,7 @@
       <c r="O275" s="17"/>
       <c r="P275" s="18"/>
     </row>
-    <row r="276" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B276" s="16" t="s">
         <v>99</v>
       </c>
@@ -19452,7 +19452,7 @@
       <c r="O276" s="17"/>
       <c r="P276" s="18"/>
     </row>
-    <row r="277" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B277" s="16" t="s">
         <v>99</v>
       </c>
@@ -19473,7 +19473,7 @@
       <c r="O277" s="17"/>
       <c r="P277" s="18"/>
     </row>
-    <row r="278" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B278" s="16" t="s">
         <v>100</v>
       </c>
@@ -19494,7 +19494,7 @@
       <c r="O278" s="17"/>
       <c r="P278" s="18"/>
     </row>
-    <row r="279" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B279" s="16" t="s">
         <v>100</v>
       </c>
@@ -19515,7 +19515,7 @@
       <c r="O279" s="17"/>
       <c r="P279" s="18"/>
     </row>
-    <row r="280" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B280" s="16" t="s">
         <v>100</v>
       </c>
@@ -19536,7 +19536,7 @@
       <c r="O280" s="17"/>
       <c r="P280" s="18"/>
     </row>
-    <row r="281" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B281" s="16" t="s">
         <v>100</v>
       </c>
@@ -19557,7 +19557,7 @@
       <c r="O281" s="17"/>
       <c r="P281" s="18"/>
     </row>
-    <row r="282" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B282" s="16" t="s">
         <v>101</v>
       </c>
@@ -19578,7 +19578,7 @@
       <c r="O282" s="17"/>
       <c r="P282" s="18"/>
     </row>
-    <row r="283" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B283" s="16" t="s">
         <v>101</v>
       </c>
@@ -19599,7 +19599,7 @@
       <c r="O283" s="17"/>
       <c r="P283" s="18"/>
     </row>
-    <row r="284" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B284" s="16" t="s">
         <v>101</v>
       </c>
@@ -19620,7 +19620,7 @@
       <c r="O284" s="17"/>
       <c r="P284" s="18"/>
     </row>
-    <row r="285" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B285" s="16" t="s">
         <v>101</v>
       </c>
@@ -19641,7 +19641,7 @@
       <c r="O285" s="17"/>
       <c r="P285" s="18"/>
     </row>
-    <row r="286" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B286" s="16" t="s">
         <v>102</v>
       </c>
@@ -19662,7 +19662,7 @@
       <c r="O286" s="17"/>
       <c r="P286" s="18"/>
     </row>
-    <row r="287" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B287" s="16" t="s">
         <v>102</v>
       </c>
@@ -19683,7 +19683,7 @@
       <c r="O287" s="17"/>
       <c r="P287" s="18"/>
     </row>
-    <row r="288" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B288" s="16" t="s">
         <v>102</v>
       </c>
@@ -19704,7 +19704,7 @@
       <c r="O288" s="17"/>
       <c r="P288" s="18"/>
     </row>
-    <row r="289" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B289" s="16" t="s">
         <v>31</v>
       </c>
@@ -19725,7 +19725,7 @@
       <c r="O289" s="17"/>
       <c r="P289" s="18"/>
     </row>
-    <row r="290" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B290" s="16" t="s">
         <v>31</v>
       </c>
@@ -19746,7 +19746,7 @@
       <c r="O290" s="17"/>
       <c r="P290" s="18"/>
     </row>
-    <row r="291" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B291" s="16" t="s">
         <v>31</v>
       </c>
@@ -19767,7 +19767,7 @@
       <c r="O291" s="17"/>
       <c r="P291" s="18"/>
     </row>
-    <row r="292" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B292" s="16" t="s">
         <v>31</v>
       </c>
@@ -19788,7 +19788,7 @@
       <c r="O292" s="17"/>
       <c r="P292" s="18"/>
     </row>
-    <row r="293" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B293" s="16" t="s">
         <v>103</v>
       </c>
@@ -19809,7 +19809,7 @@
       <c r="O293" s="17"/>
       <c r="P293" s="18"/>
     </row>
-    <row r="294" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B294" s="16" t="s">
         <v>103</v>
       </c>
@@ -19830,7 +19830,7 @@
       <c r="O294" s="17"/>
       <c r="P294" s="18"/>
     </row>
-    <row r="295" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B295" s="16" t="s">
         <v>103</v>
       </c>
@@ -19851,7 +19851,7 @@
       <c r="O295" s="17"/>
       <c r="P295" s="18"/>
     </row>
-    <row r="296" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B296" s="16" t="s">
         <v>104</v>
       </c>
@@ -19872,7 +19872,7 @@
       <c r="O296" s="17"/>
       <c r="P296" s="18"/>
     </row>
-    <row r="297" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B297" s="16" t="s">
         <v>104</v>
       </c>
@@ -19893,7 +19893,7 @@
       <c r="O297" s="17"/>
       <c r="P297" s="18"/>
     </row>
-    <row r="298" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B298" s="16" t="s">
         <v>104</v>
       </c>
@@ -19914,7 +19914,7 @@
       <c r="O298" s="17"/>
       <c r="P298" s="18"/>
     </row>
-    <row r="299" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B299" s="16" t="s">
         <v>105</v>
       </c>
@@ -19935,7 +19935,7 @@
       <c r="O299" s="17"/>
       <c r="P299" s="18"/>
     </row>
-    <row r="300" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B300" s="16" t="s">
         <v>105</v>
       </c>
@@ -19956,7 +19956,7 @@
       <c r="O300" s="17"/>
       <c r="P300" s="18"/>
     </row>
-    <row r="301" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B301" s="16" t="s">
         <v>105</v>
       </c>
@@ -19977,7 +19977,7 @@
       <c r="O301" s="17"/>
       <c r="P301" s="18"/>
     </row>
-    <row r="302" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B302" s="16" t="s">
         <v>105</v>
       </c>
@@ -19998,7 +19998,7 @@
       <c r="O302" s="17"/>
       <c r="P302" s="18"/>
     </row>
-    <row r="303" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B303" s="16" t="s">
         <v>106</v>
       </c>
@@ -20019,7 +20019,7 @@
       <c r="O303" s="17"/>
       <c r="P303" s="18"/>
     </row>
-    <row r="304" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B304" s="16" t="s">
         <v>106</v>
       </c>
@@ -20040,7 +20040,7 @@
       <c r="O304" s="17"/>
       <c r="P304" s="18"/>
     </row>
-    <row r="305" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B305" s="16" t="s">
         <v>106</v>
       </c>
@@ -20061,7 +20061,7 @@
       <c r="O305" s="17"/>
       <c r="P305" s="18"/>
     </row>
-    <row r="306" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B306" s="16" t="s">
         <v>107</v>
       </c>
@@ -20082,7 +20082,7 @@
       <c r="O306" s="17"/>
       <c r="P306" s="18"/>
     </row>
-    <row r="307" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B307" s="16" t="s">
         <v>107</v>
       </c>
@@ -20103,7 +20103,7 @@
       <c r="O307" s="17"/>
       <c r="P307" s="18"/>
     </row>
-    <row r="308" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B308" s="16" t="s">
         <v>107</v>
       </c>
@@ -20124,7 +20124,7 @@
       <c r="O308" s="17"/>
       <c r="P308" s="18"/>
     </row>
-    <row r="309" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B309" s="16" t="s">
         <v>108</v>
       </c>
@@ -20145,7 +20145,7 @@
       <c r="O309" s="17"/>
       <c r="P309" s="18"/>
     </row>
-    <row r="310" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B310" s="16" t="s">
         <v>108</v>
       </c>
@@ -20166,7 +20166,7 @@
       <c r="O310" s="17"/>
       <c r="P310" s="18"/>
     </row>
-    <row r="311" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B311" s="16" t="s">
         <v>108</v>
       </c>
@@ -20187,7 +20187,7 @@
       <c r="O311" s="17"/>
       <c r="P311" s="18"/>
     </row>
-    <row r="312" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B312" s="16" t="s">
         <v>109</v>
       </c>
@@ -20208,7 +20208,7 @@
       <c r="O312" s="17"/>
       <c r="P312" s="18"/>
     </row>
-    <row r="313" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B313" s="16" t="s">
         <v>109</v>
       </c>
@@ -20229,7 +20229,7 @@
       <c r="O313" s="17"/>
       <c r="P313" s="18"/>
     </row>
-    <row r="314" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B314" s="16" t="s">
         <v>109</v>
       </c>
@@ -20250,7 +20250,7 @@
       <c r="O314" s="17"/>
       <c r="P314" s="18"/>
     </row>
-    <row r="315" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B315" s="16" t="s">
         <v>110</v>
       </c>
@@ -20271,7 +20271,7 @@
       <c r="O315" s="17"/>
       <c r="P315" s="18"/>
     </row>
-    <row r="316" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B316" s="16" t="s">
         <v>110</v>
       </c>
@@ -20292,7 +20292,7 @@
       <c r="O316" s="17"/>
       <c r="P316" s="18"/>
     </row>
-    <row r="317" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B317" s="16" t="s">
         <v>110</v>
       </c>
@@ -20313,7 +20313,7 @@
       <c r="O317" s="17"/>
       <c r="P317" s="18"/>
     </row>
-    <row r="318" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B318" s="16" t="s">
         <v>111</v>
       </c>
@@ -20334,7 +20334,7 @@
       <c r="O318" s="17"/>
       <c r="P318" s="18"/>
     </row>
-    <row r="319" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B319" s="16" t="s">
         <v>111</v>
       </c>
@@ -20355,7 +20355,7 @@
       <c r="O319" s="17"/>
       <c r="P319" s="18"/>
     </row>
-    <row r="320" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B320" s="16" t="s">
         <v>111</v>
       </c>
@@ -20376,7 +20376,7 @@
       <c r="O320" s="17"/>
       <c r="P320" s="18"/>
     </row>
-    <row r="321" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="321" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B321" s="16" t="s">
         <v>111</v>
       </c>
@@ -20397,7 +20397,7 @@
       <c r="O321" s="17"/>
       <c r="P321" s="18"/>
     </row>
-    <row r="322" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B322" s="16" t="s">
         <v>91</v>
       </c>
@@ -20418,7 +20418,7 @@
       <c r="O322" s="17"/>
       <c r="P322" s="18"/>
     </row>
-    <row r="323" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B323" s="16" t="s">
         <v>91</v>
       </c>
@@ -20439,7 +20439,7 @@
       <c r="O323" s="17"/>
       <c r="P323" s="18"/>
     </row>
-    <row r="324" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B324" s="16" t="s">
         <v>91</v>
       </c>
@@ -20460,7 +20460,7 @@
       <c r="O324" s="17"/>
       <c r="P324" s="18"/>
     </row>
-    <row r="325" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B325" s="16" t="s">
         <v>91</v>
       </c>
@@ -20481,7 +20481,7 @@
       <c r="O325" s="17"/>
       <c r="P325" s="18"/>
     </row>
-    <row r="326" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B326" s="16" t="s">
         <v>92</v>
       </c>
@@ -20502,7 +20502,7 @@
       <c r="O326" s="17"/>
       <c r="P326" s="18"/>
     </row>
-    <row r="327" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B327" s="16" t="s">
         <v>92</v>
       </c>
@@ -20523,7 +20523,7 @@
       <c r="O327" s="17"/>
       <c r="P327" s="18"/>
     </row>
-    <row r="328" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B328" s="16" t="s">
         <v>92</v>
       </c>
@@ -20544,7 +20544,7 @@
       <c r="O328" s="17"/>
       <c r="P328" s="18"/>
     </row>
-    <row r="329" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B329" s="16" t="s">
         <v>92</v>
       </c>
@@ -20565,7 +20565,7 @@
       <c r="O329" s="17"/>
       <c r="P329" s="18"/>
     </row>
-    <row r="330" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B330" s="16" t="s">
         <v>93</v>
       </c>
@@ -20586,7 +20586,7 @@
       <c r="O330" s="17"/>
       <c r="P330" s="18"/>
     </row>
-    <row r="331" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B331" s="16" t="s">
         <v>93</v>
       </c>
@@ -20607,7 +20607,7 @@
       <c r="O331" s="17"/>
       <c r="P331" s="18"/>
     </row>
-    <row r="332" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B332" s="16" t="s">
         <v>93</v>
       </c>
@@ -20628,7 +20628,7 @@
       <c r="O332" s="17"/>
       <c r="P332" s="18"/>
     </row>
-    <row r="333" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B333" s="16" t="s">
         <v>93</v>
       </c>
@@ -20649,7 +20649,7 @@
       <c r="O333" s="17"/>
       <c r="P333" s="18"/>
     </row>
-    <row r="334" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B334" s="16" t="s">
         <v>94</v>
       </c>
@@ -20670,7 +20670,7 @@
       <c r="O334" s="17"/>
       <c r="P334" s="18"/>
     </row>
-    <row r="335" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B335" s="16" t="s">
         <v>94</v>
       </c>
@@ -20691,7 +20691,7 @@
       <c r="O335" s="17"/>
       <c r="P335" s="18"/>
     </row>
-    <row r="336" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B336" s="16" t="s">
         <v>94</v>
       </c>
@@ -20712,7 +20712,7 @@
       <c r="O336" s="17"/>
       <c r="P336" s="18"/>
     </row>
-    <row r="337" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B337" s="16" t="s">
         <v>94</v>
       </c>
@@ -20733,7 +20733,7 @@
       <c r="O337" s="17"/>
       <c r="P337" s="18"/>
     </row>
-    <row r="338" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B338" s="16" t="s">
         <v>95</v>
       </c>
@@ -20754,7 +20754,7 @@
       <c r="O338" s="17"/>
       <c r="P338" s="18"/>
     </row>
-    <row r="339" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B339" s="16" t="s">
         <v>95</v>
       </c>
@@ -20775,7 +20775,7 @@
       <c r="O339" s="17"/>
       <c r="P339" s="18"/>
     </row>
-    <row r="340" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B340" s="16" t="s">
         <v>95</v>
       </c>
@@ -20796,7 +20796,7 @@
       <c r="O340" s="17"/>
       <c r="P340" s="18"/>
     </row>
-    <row r="341" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B341" s="16" t="s">
         <v>95</v>
       </c>
@@ -20817,7 +20817,7 @@
       <c r="O341" s="17"/>
       <c r="P341" s="18"/>
     </row>
-    <row r="342" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B342" s="16" t="s">
         <v>96</v>
       </c>
@@ -20838,7 +20838,7 @@
       <c r="O342" s="17"/>
       <c r="P342" s="18"/>
     </row>
-    <row r="343" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B343" s="16" t="s">
         <v>96</v>
       </c>
@@ -20859,7 +20859,7 @@
       <c r="O343" s="17"/>
       <c r="P343" s="18"/>
     </row>
-    <row r="344" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B344" s="16" t="s">
         <v>96</v>
       </c>
@@ -20880,7 +20880,7 @@
       <c r="O344" s="17"/>
       <c r="P344" s="18"/>
     </row>
-    <row r="345" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B345" s="16" t="s">
         <v>97</v>
       </c>
@@ -20901,7 +20901,7 @@
       <c r="O345" s="17"/>
       <c r="P345" s="18"/>
     </row>
-    <row r="346" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B346" s="16" t="s">
         <v>97</v>
       </c>
@@ -20922,7 +20922,7 @@
       <c r="O346" s="17"/>
       <c r="P346" s="18"/>
     </row>
-    <row r="347" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B347" s="16" t="s">
         <v>97</v>
       </c>
@@ -20943,7 +20943,7 @@
       <c r="O347" s="17"/>
       <c r="P347" s="18"/>
     </row>
-    <row r="348" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B348" s="16" t="s">
         <v>97</v>
       </c>
@@ -20964,7 +20964,7 @@
       <c r="O348" s="17"/>
       <c r="P348" s="18"/>
     </row>
-    <row r="349" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B349" s="16" t="s">
         <v>98</v>
       </c>
@@ -20985,7 +20985,7 @@
       <c r="O349" s="17"/>
       <c r="P349" s="18"/>
     </row>
-    <row r="350" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B350" s="16" t="s">
         <v>98</v>
       </c>
@@ -21006,7 +21006,7 @@
       <c r="O350" s="17"/>
       <c r="P350" s="18"/>
     </row>
-    <row r="351" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B351" s="16" t="s">
         <v>98</v>
       </c>
@@ -21027,7 +21027,7 @@
       <c r="O351" s="17"/>
       <c r="P351" s="18"/>
     </row>
-    <row r="352" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B352" s="16" t="s">
         <v>98</v>
       </c>
@@ -21048,7 +21048,7 @@
       <c r="O352" s="17"/>
       <c r="P352" s="18"/>
     </row>
-    <row r="353" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B353" s="16" t="s">
         <v>99</v>
       </c>
@@ -21069,7 +21069,7 @@
       <c r="O353" s="17"/>
       <c r="P353" s="18"/>
     </row>
-    <row r="354" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B354" s="16" t="s">
         <v>99</v>
       </c>
@@ -21090,7 +21090,7 @@
       <c r="O354" s="17"/>
       <c r="P354" s="18"/>
     </row>
-    <row r="355" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B355" s="16" t="s">
         <v>99</v>
       </c>
@@ -21111,7 +21111,7 @@
       <c r="O355" s="17"/>
       <c r="P355" s="18"/>
     </row>
-    <row r="356" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B356" s="16" t="s">
         <v>99</v>
       </c>
@@ -21132,7 +21132,7 @@
       <c r="O356" s="17"/>
       <c r="P356" s="18"/>
     </row>
-    <row r="357" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B357" s="16" t="s">
         <v>100</v>
       </c>
@@ -21153,7 +21153,7 @@
       <c r="O357" s="17"/>
       <c r="P357" s="18"/>
     </row>
-    <row r="358" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B358" s="16" t="s">
         <v>100</v>
       </c>
@@ -21174,7 +21174,7 @@
       <c r="O358" s="17"/>
       <c r="P358" s="18"/>
     </row>
-    <row r="359" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B359" s="16" t="s">
         <v>100</v>
       </c>
@@ -21195,7 +21195,7 @@
       <c r="O359" s="17"/>
       <c r="P359" s="18"/>
     </row>
-    <row r="360" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B360" s="16" t="s">
         <v>100</v>
       </c>
@@ -21216,7 +21216,7 @@
       <c r="O360" s="17"/>
       <c r="P360" s="18"/>
     </row>
-    <row r="361" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B361" s="16" t="s">
         <v>101</v>
       </c>
@@ -21237,7 +21237,7 @@
       <c r="O361" s="17"/>
       <c r="P361" s="18"/>
     </row>
-    <row r="362" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B362" s="16" t="s">
         <v>101</v>
       </c>
@@ -21258,7 +21258,7 @@
       <c r="O362" s="17"/>
       <c r="P362" s="18"/>
     </row>
-    <row r="363" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B363" s="16" t="s">
         <v>101</v>
       </c>
@@ -21279,7 +21279,7 @@
       <c r="O363" s="17"/>
       <c r="P363" s="18"/>
     </row>
-    <row r="364" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B364" s="16" t="s">
         <v>101</v>
       </c>
@@ -21300,7 +21300,7 @@
       <c r="O364" s="17"/>
       <c r="P364" s="18"/>
     </row>
-    <row r="365" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B365" s="16" t="s">
         <v>112</v>
       </c>
@@ -21321,7 +21321,7 @@
       <c r="O365" s="17"/>
       <c r="P365" s="18"/>
     </row>
-    <row r="366" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B366" s="16" t="s">
         <v>112</v>
       </c>
@@ -21342,7 +21342,7 @@
       <c r="O366" s="17"/>
       <c r="P366" s="18"/>
     </row>
-    <row r="367" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B367" s="16" t="s">
         <v>112</v>
       </c>
@@ -21363,7 +21363,7 @@
       <c r="O367" s="17"/>
       <c r="P367" s="18"/>
     </row>
-    <row r="368" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B368" s="16" t="s">
         <v>112</v>
       </c>
@@ -21384,7 +21384,7 @@
       <c r="O368" s="17"/>
       <c r="P368" s="18"/>
     </row>
-    <row r="369" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B369" s="16" t="s">
         <v>113</v>
       </c>
@@ -21405,7 +21405,7 @@
       <c r="O369" s="17"/>
       <c r="P369" s="18"/>
     </row>
-    <row r="370" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B370" s="16" t="s">
         <v>113</v>
       </c>
@@ -21426,7 +21426,7 @@
       <c r="O370" s="17"/>
       <c r="P370" s="18"/>
     </row>
-    <row r="371" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B371" s="16" t="s">
         <v>113</v>
       </c>
@@ -21447,7 +21447,7 @@
       <c r="O371" s="17"/>
       <c r="P371" s="18"/>
     </row>
-    <row r="372" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B372" s="16" t="s">
         <v>114</v>
       </c>
@@ -21468,7 +21468,7 @@
       <c r="O372" s="17"/>
       <c r="P372" s="18"/>
     </row>
-    <row r="373" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B373" s="16" t="s">
         <v>114</v>
       </c>
@@ -21489,7 +21489,7 @@
       <c r="O373" s="17"/>
       <c r="P373" s="18"/>
     </row>
-    <row r="374" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B374" s="16" t="s">
         <v>114</v>
       </c>
@@ -21510,7 +21510,7 @@
       <c r="O374" s="17"/>
       <c r="P374" s="18"/>
     </row>
-    <row r="375" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B375" s="16" t="s">
         <v>114</v>
       </c>
@@ -21531,7 +21531,7 @@
       <c r="O375" s="17"/>
       <c r="P375" s="18"/>
     </row>
-    <row r="376" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B376" s="16" t="s">
         <v>115</v>
       </c>
@@ -21552,7 +21552,7 @@
       <c r="O376" s="17"/>
       <c r="P376" s="18"/>
     </row>
-    <row r="377" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B377" s="16" t="s">
         <v>115</v>
       </c>
@@ -21573,7 +21573,7 @@
       <c r="O377" s="17"/>
       <c r="P377" s="18"/>
     </row>
-    <row r="378" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B378" s="16" t="s">
         <v>115</v>
       </c>
@@ -21594,7 +21594,7 @@
       <c r="O378" s="17"/>
       <c r="P378" s="18"/>
     </row>
-    <row r="379" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B379" s="16" t="s">
         <v>115</v>
       </c>
@@ -21615,7 +21615,7 @@
       <c r="O379" s="17"/>
       <c r="P379" s="18"/>
     </row>
-    <row r="380" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B380" s="16" t="s">
         <v>116</v>
       </c>
@@ -21636,7 +21636,7 @@
       <c r="O380" s="17"/>
       <c r="P380" s="18"/>
     </row>
-    <row r="381" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B381" s="16" t="s">
         <v>116</v>
       </c>
@@ -21657,7 +21657,7 @@
       <c r="O381" s="17"/>
       <c r="P381" s="18"/>
     </row>
-    <row r="382" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B382" s="16" t="s">
         <v>116</v>
       </c>
@@ -21678,7 +21678,7 @@
       <c r="O382" s="17"/>
       <c r="P382" s="18"/>
     </row>
-    <row r="383" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B383" s="16" t="s">
         <v>117</v>
       </c>
@@ -21699,7 +21699,7 @@
       <c r="O383" s="17"/>
       <c r="P383" s="18"/>
     </row>
-    <row r="384" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B384" s="16" t="s">
         <v>117</v>
       </c>
@@ -21720,7 +21720,7 @@
       <c r="O384" s="17"/>
       <c r="P384" s="18"/>
     </row>
-    <row r="385" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B385" s="16" t="s">
         <v>117</v>
       </c>
@@ -21741,7 +21741,7 @@
       <c r="O385" s="17"/>
       <c r="P385" s="18"/>
     </row>
-    <row r="386" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B386" s="16" t="s">
         <v>117</v>
       </c>
@@ -21762,7 +21762,7 @@
       <c r="O386" s="17"/>
       <c r="P386" s="18"/>
     </row>
-    <row r="387" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B387" s="16" t="s">
         <v>118</v>
       </c>
@@ -21783,7 +21783,7 @@
       <c r="O387" s="17"/>
       <c r="P387" s="18"/>
     </row>
-    <row r="388" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B388" s="16" t="s">
         <v>118</v>
       </c>
@@ -21804,7 +21804,7 @@
       <c r="O388" s="17"/>
       <c r="P388" s="18"/>
     </row>
-    <row r="389" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B389" s="16" t="s">
         <v>118</v>
       </c>
@@ -21825,7 +21825,7 @@
       <c r="O389" s="17"/>
       <c r="P389" s="18"/>
     </row>
-    <row r="390" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B390" s="16" t="s">
         <v>119</v>
       </c>
@@ -21846,7 +21846,7 @@
       <c r="O390" s="17"/>
       <c r="P390" s="18"/>
     </row>
-    <row r="391" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B391" s="16" t="s">
         <v>119</v>
       </c>
@@ -21867,7 +21867,7 @@
       <c r="O391" s="17"/>
       <c r="P391" s="18"/>
     </row>
-    <row r="392" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B392" s="16" t="s">
         <v>119</v>
       </c>
@@ -21888,7 +21888,7 @@
       <c r="O392" s="17"/>
       <c r="P392" s="18"/>
     </row>
-    <row r="393" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B393" s="16" t="s">
         <v>120</v>
       </c>
@@ -21909,7 +21909,7 @@
       <c r="O393" s="17"/>
       <c r="P393" s="18"/>
     </row>
-    <row r="394" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B394" s="16" t="s">
         <v>120</v>
       </c>
@@ -21930,7 +21930,7 @@
       <c r="O394" s="17"/>
       <c r="P394" s="18"/>
     </row>
-    <row r="395" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B395" s="16" t="s">
         <v>120</v>
       </c>
@@ -21951,7 +21951,7 @@
       <c r="O395" s="17"/>
       <c r="P395" s="18"/>
     </row>
-    <row r="396" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B396" s="16" t="s">
         <v>121</v>
       </c>
@@ -21972,7 +21972,7 @@
       <c r="O396" s="17"/>
       <c r="P396" s="18"/>
     </row>
-    <row r="397" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B397" s="16" t="s">
         <v>121</v>
       </c>
@@ -21993,7 +21993,7 @@
       <c r="O397" s="17"/>
       <c r="P397" s="18"/>
     </row>
-    <row r="398" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B398" s="16" t="s">
         <v>121</v>
       </c>
@@ -22014,7 +22014,7 @@
       <c r="O398" s="17"/>
       <c r="P398" s="18"/>
     </row>
-    <row r="399" spans="2:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B399" s="25" t="s">
         <v>121</v>
       </c>
